--- a/docs/582-511-web5/projets/portfolio/qa-gabarit-portfolio.xlsx
+++ b/docs/582-511-web5/projets/portfolio/qa-gabarit-portfolio.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="190">
   <si>
     <t xml:space="preserve">Contrôle de la qualité du portfolio</t>
   </si>
@@ -42,10 +42,7 @@
     <t xml:space="preserve">Groupe (Lora ou Enric)</t>
   </si>
   <si>
-    <t xml:space="preserve">Adresse de la bêta (branche beta)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adresse finale (branche main)</t>
+    <t xml:space="preserve">Adresse du site (GitHub Pages)</t>
   </si>
   <si>
     <t xml:space="preserve">Dépôt GitHub</t>
@@ -87,7 +84,7 @@
     <t xml:space="preserve">1. Remplissez les cellules jaunes ci-dessus. Ajoutez 2 ou 3 scénarios personnels dans l'onglet Scénarios (scénarios 12 à 14).</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Les tests se font sur l'adresse de la BÊTA (branche beta). Chaque testeur fait tous les scénarios, dans l'onglet Tests, dans son bloc.</t>
+    <t xml:space="preserve">2. Les tests se font sur l'adresse de votre site, pendant que GitHub Pages publie encore la branche beta. Chaque testeur fait tous les scénarios, dans l'onglet Tests, dans son bloc.</t>
   </si>
   <si>
     <t xml:space="preserve">3. Pour chaque ligne : Résultat = Conforme ou Écart. Si Écart : décrivez ce que vous observez et choisissez une gravité.</t>
@@ -165,7 +162,7 @@
     <t xml:space="preserve">Validation</t>
   </si>
   <si>
-    <t xml:space="preserve">Scénario 7 refait le 6 oct. sur l'adresse finale (main), Firefox : focus visible partout, Échap ferme la modale. Validé : Oui</t>
+    <t xml:space="preserve">Scénario 7 refait le 6 oct. en ligne (Pages sur main), Firefox : focus visible partout, Échap ferme la modale. Validé : Oui</t>
   </si>
   <si>
     <t xml:space="preserve">Scénarios de test</t>
@@ -321,7 +318,7 @@
     <t xml:space="preserve">Résultats des tests</t>
   </si>
   <si>
-    <t xml:space="preserve">Tests faits sur l'adresse de la BÊTA. Chaque testeur remplit son bloc. Cellules jaunes = à remplir.</t>
+    <t xml:space="preserve">Tests faits pendant que le site publie la branche beta. Chaque testeur remplit son bloc. Cellules jaunes = à remplir.</t>
   </si>
   <si>
     <t xml:space="preserve">ID</t>
@@ -462,7 +459,7 @@
     <t xml:space="preserve">Correctifs et validation</t>
   </si>
   <si>
-    <t xml:space="preserve">Un écart = une ligne. Corrigez sur main, puis validez en refaisant le scénario EN LIGNE, sur l'adresse finale.</t>
+    <t xml:space="preserve">Un écart = une ligne. Corrigez sur main, puis validez en refaisant le scénario EN LIGNE, une fois GitHub Pages passé sur main.</t>
   </si>
   <si>
     <t xml:space="preserve">ID du test</t>
@@ -1119,7 +1116,7 @@
     <tabColor rgb="FF0A0A0A"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1176,50 +1173,52 @@
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="B11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="E11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="6" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="F13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
@@ -1231,20 +1230,20 @@
       <c r="E14" s="5"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
         <v>18</v>
       </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
@@ -1296,27 +1295,29 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="B25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -1325,36 +1326,36 @@
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
     </row>
-    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="9" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="B30" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>34</v>
@@ -1366,63 +1367,63 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
     </row>
-    <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="B37" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
@@ -1431,52 +1432,39 @@
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
     </row>
-    <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="21">
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="B25:F25"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B30:F30"/>
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B37:F37"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B40:F40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1506,29 +1494,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1536,16 +1524,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1553,16 +1541,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1570,16 +1558,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1587,16 +1575,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1604,16 +1592,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1621,16 +1609,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="D10" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1638,16 +1626,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1655,16 +1643,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="D12" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1672,16 +1660,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="D13" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1689,16 +1677,16 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>90</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1706,16 +1694,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1726,7 +1714,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1737,7 +1725,7 @@
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1748,7 +1736,7 @@
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1783,43 +1771,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>101</v>
-      </c>
       <c r="H4" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="str">
-        <f aca="false">"Testeur 1 : "&amp;IF('Lisez-moi'!B13="","(nom à inscrire dans Lisez-moi)",'Lisez-moi'!B13)</f>
+        <f aca="false">"Testeur 1 : "&amp;IF('Lisez-moi'!B12="","(nom à inscrire dans Lisez-moi)",'Lisez-moi'!B12)</f>
         <v>Testeur 1 : (nom à inscrire dans Lisez-moi)</v>
       </c>
       <c r="B5" s="13"/>
@@ -1832,7 +1820,7 @@
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>1</v>
@@ -1842,11 +1830,11 @@
         <v>Première impression</v>
       </c>
       <c r="D6" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 1",'Lisez-moi'!$B$13)</f>
+        <f aca="false">IF('Lisez-moi'!$B$12="","Testeur 1",'Lisez-moi'!$B$12)</f>
         <v>Testeur 1</v>
       </c>
       <c r="E6" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
       <c r="F6" s="14"/>
@@ -1855,7 +1843,7 @@
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>2</v>
@@ -1865,11 +1853,11 @@
         <v>Navigation par le menu</v>
       </c>
       <c r="D7" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 1",'Lisez-moi'!$B$13)</f>
+        <f aca="false">IF('Lisez-moi'!$B$12="","Testeur 1",'Lisez-moi'!$B$12)</f>
         <v>Testeur 1</v>
       </c>
       <c r="E7" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
       <c r="F7" s="14"/>
@@ -1878,7 +1866,7 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>3</v>
@@ -1888,11 +1876,11 @@
         <v>Liste des projets</v>
       </c>
       <c r="D8" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 1",'Lisez-moi'!$B$13)</f>
+        <f aca="false">IF('Lisez-moi'!$B$12="","Testeur 1",'Lisez-moi'!$B$12)</f>
         <v>Testeur 1</v>
       </c>
       <c r="E8" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
       <c r="F8" s="14"/>
@@ -1901,7 +1889,7 @@
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>4</v>
@@ -1911,11 +1899,11 @@
         <v>Détail d'un projet</v>
       </c>
       <c r="D9" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 1",'Lisez-moi'!$B$13)</f>
+        <f aca="false">IF('Lisez-moi'!$B$12="","Testeur 1",'Lisez-moi'!$B$12)</f>
         <v>Testeur 1</v>
       </c>
       <c r="E9" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
       <c r="F9" s="14"/>
@@ -1924,7 +1912,7 @@
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>5</v>
@@ -1934,11 +1922,11 @@
         <v>Liens externes et contact</v>
       </c>
       <c r="D10" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 1",'Lisez-moi'!$B$13)</f>
+        <f aca="false">IF('Lisez-moi'!$B$12="","Testeur 1",'Lisez-moi'!$B$12)</f>
         <v>Testeur 1</v>
       </c>
       <c r="E10" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
       <c r="F10" s="14"/>
@@ -1947,7 +1935,7 @@
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>6</v>
@@ -1957,11 +1945,11 @@
         <v>Version mobile</v>
       </c>
       <c r="D11" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 1",'Lisez-moi'!$B$13)</f>
+        <f aca="false">IF('Lisez-moi'!$B$12="","Testeur 1",'Lisez-moi'!$B$12)</f>
         <v>Testeur 1</v>
       </c>
       <c r="E11" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
       <c r="F11" s="14"/>
@@ -1970,7 +1958,7 @@
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>7</v>
@@ -1980,11 +1968,11 @@
         <v>Navigation au clavier</v>
       </c>
       <c r="D12" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 1",'Lisez-moi'!$B$13)</f>
+        <f aca="false">IF('Lisez-moi'!$B$12="","Testeur 1",'Lisez-moi'!$B$12)</f>
         <v>Testeur 1</v>
       </c>
       <c r="E12" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
       <c r="F12" s="14"/>
@@ -1993,7 +1981,7 @@
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>8</v>
@@ -2003,11 +1991,11 @@
         <v>Contraste des textes</v>
       </c>
       <c r="D13" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 1",'Lisez-moi'!$B$13)</f>
+        <f aca="false">IF('Lisez-moi'!$B$12="","Testeur 1",'Lisez-moi'!$B$12)</f>
         <v>Testeur 1</v>
       </c>
       <c r="E13" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
       <c r="F13" s="14"/>
@@ -2016,7 +2004,7 @@
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>9</v>
@@ -2026,11 +2014,11 @@
         <v>Structure et textes alternatifs</v>
       </c>
       <c r="D14" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 1",'Lisez-moi'!$B$13)</f>
+        <f aca="false">IF('Lisez-moi'!$B$12="","Testeur 1",'Lisez-moi'!$B$12)</f>
         <v>Testeur 1</v>
       </c>
       <c r="E14" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
       <c r="F14" s="14"/>
@@ -2039,7 +2027,7 @@
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>10</v>
@@ -2049,11 +2037,11 @@
         <v>Console et réseau</v>
       </c>
       <c r="D15" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 1",'Lisez-moi'!$B$13)</f>
+        <f aca="false">IF('Lisez-moi'!$B$12="","Testeur 1",'Lisez-moi'!$B$12)</f>
         <v>Testeur 1</v>
       </c>
       <c r="E15" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
       <c r="F15" s="14"/>
@@ -2062,7 +2050,7 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>11</v>
@@ -2072,11 +2060,11 @@
         <v>Chargement sur connexion lente</v>
       </c>
       <c r="D16" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 1",'Lisez-moi'!$B$13)</f>
+        <f aca="false">IF('Lisez-moi'!$B$12="","Testeur 1",'Lisez-moi'!$B$12)</f>
         <v>Testeur 1</v>
       </c>
       <c r="E16" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
       <c r="F16" s="14"/>
@@ -2085,7 +2073,7 @@
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B17" s="12" t="n">
         <v>12</v>
@@ -2095,11 +2083,11 @@
         <v>(scénario personnel à définir)</v>
       </c>
       <c r="D17" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 1",'Lisez-moi'!$B$13)</f>
+        <f aca="false">IF('Lisez-moi'!$B$12="","Testeur 1",'Lisez-moi'!$B$12)</f>
         <v>Testeur 1</v>
       </c>
       <c r="E17" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
       <c r="F17" s="14"/>
@@ -2108,7 +2096,7 @@
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>13</v>
@@ -2118,11 +2106,11 @@
         <v>(scénario personnel à définir)</v>
       </c>
       <c r="D18" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 1",'Lisez-moi'!$B$13)</f>
+        <f aca="false">IF('Lisez-moi'!$B$12="","Testeur 1",'Lisez-moi'!$B$12)</f>
         <v>Testeur 1</v>
       </c>
       <c r="E18" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
       <c r="F18" s="14"/>
@@ -2131,7 +2119,7 @@
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B19" s="12" t="n">
         <v>14</v>
@@ -2141,11 +2129,11 @@
         <v>(scénario personnel à définir)</v>
       </c>
       <c r="D19" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 1",'Lisez-moi'!$B$13)</f>
+        <f aca="false">IF('Lisez-moi'!$B$12="","Testeur 1",'Lisez-moi'!$B$12)</f>
         <v>Testeur 1</v>
       </c>
       <c r="E19" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
       <c r="F19" s="14"/>
@@ -2154,7 +2142,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="str">
-        <f aca="false">"Testeur 2 : "&amp;IF('Lisez-moi'!B14="","(nom à inscrire dans Lisez-moi)",'Lisez-moi'!B14)</f>
+        <f aca="false">"Testeur 2 : "&amp;IF('Lisez-moi'!B13="","(nom à inscrire dans Lisez-moi)",'Lisez-moi'!B13)</f>
         <v>Testeur 2 : (nom à inscrire dans Lisez-moi)</v>
       </c>
       <c r="B20" s="13"/>
@@ -2167,7 +2155,7 @@
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B21" s="12" t="n">
         <v>1</v>
@@ -2177,11 +2165,11 @@
         <v>Première impression</v>
       </c>
       <c r="D21" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 2",'Lisez-moi'!$B$14)</f>
+        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 2",'Lisez-moi'!$B$13)</f>
         <v>Testeur 2</v>
       </c>
       <c r="E21" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
       <c r="F21" s="14"/>
@@ -2190,7 +2178,7 @@
     </row>
     <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B22" s="12" t="n">
         <v>2</v>
@@ -2200,11 +2188,11 @@
         <v>Navigation par le menu</v>
       </c>
       <c r="D22" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 2",'Lisez-moi'!$B$14)</f>
+        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 2",'Lisez-moi'!$B$13)</f>
         <v>Testeur 2</v>
       </c>
       <c r="E22" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
       <c r="F22" s="14"/>
@@ -2213,7 +2201,7 @@
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B23" s="12" t="n">
         <v>3</v>
@@ -2223,11 +2211,11 @@
         <v>Liste des projets</v>
       </c>
       <c r="D23" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 2",'Lisez-moi'!$B$14)</f>
+        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 2",'Lisez-moi'!$B$13)</f>
         <v>Testeur 2</v>
       </c>
       <c r="E23" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
       <c r="F23" s="14"/>
@@ -2236,7 +2224,7 @@
     </row>
     <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>4</v>
@@ -2246,11 +2234,11 @@
         <v>Détail d'un projet</v>
       </c>
       <c r="D24" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 2",'Lisez-moi'!$B$14)</f>
+        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 2",'Lisez-moi'!$B$13)</f>
         <v>Testeur 2</v>
       </c>
       <c r="E24" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
       <c r="F24" s="14"/>
@@ -2259,7 +2247,7 @@
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>5</v>
@@ -2269,11 +2257,11 @@
         <v>Liens externes et contact</v>
       </c>
       <c r="D25" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 2",'Lisez-moi'!$B$14)</f>
+        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 2",'Lisez-moi'!$B$13)</f>
         <v>Testeur 2</v>
       </c>
       <c r="E25" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
       <c r="F25" s="14"/>
@@ -2282,7 +2270,7 @@
     </row>
     <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>6</v>
@@ -2292,11 +2280,11 @@
         <v>Version mobile</v>
       </c>
       <c r="D26" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 2",'Lisez-moi'!$B$14)</f>
+        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 2",'Lisez-moi'!$B$13)</f>
         <v>Testeur 2</v>
       </c>
       <c r="E26" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
       <c r="F26" s="14"/>
@@ -2305,7 +2293,7 @@
     </row>
     <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>7</v>
@@ -2315,11 +2303,11 @@
         <v>Navigation au clavier</v>
       </c>
       <c r="D27" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 2",'Lisez-moi'!$B$14)</f>
+        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 2",'Lisez-moi'!$B$13)</f>
         <v>Testeur 2</v>
       </c>
       <c r="E27" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
       <c r="F27" s="14"/>
@@ -2328,7 +2316,7 @@
     </row>
     <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>8</v>
@@ -2338,11 +2326,11 @@
         <v>Contraste des textes</v>
       </c>
       <c r="D28" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 2",'Lisez-moi'!$B$14)</f>
+        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 2",'Lisez-moi'!$B$13)</f>
         <v>Testeur 2</v>
       </c>
       <c r="E28" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
       <c r="F28" s="14"/>
@@ -2351,7 +2339,7 @@
     </row>
     <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>9</v>
@@ -2361,11 +2349,11 @@
         <v>Structure et textes alternatifs</v>
       </c>
       <c r="D29" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 2",'Lisez-moi'!$B$14)</f>
+        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 2",'Lisez-moi'!$B$13)</f>
         <v>Testeur 2</v>
       </c>
       <c r="E29" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
       <c r="F29" s="14"/>
@@ -2374,7 +2362,7 @@
     </row>
     <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>10</v>
@@ -2384,11 +2372,11 @@
         <v>Console et réseau</v>
       </c>
       <c r="D30" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 2",'Lisez-moi'!$B$14)</f>
+        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 2",'Lisez-moi'!$B$13)</f>
         <v>Testeur 2</v>
       </c>
       <c r="E30" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
       <c r="F30" s="14"/>
@@ -2397,7 +2385,7 @@
     </row>
     <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B31" s="12" t="n">
         <v>11</v>
@@ -2407,11 +2395,11 @@
         <v>Chargement sur connexion lente</v>
       </c>
       <c r="D31" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 2",'Lisez-moi'!$B$14)</f>
+        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 2",'Lisez-moi'!$B$13)</f>
         <v>Testeur 2</v>
       </c>
       <c r="E31" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
       <c r="F31" s="14"/>
@@ -2420,7 +2408,7 @@
     </row>
     <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B32" s="12" t="n">
         <v>12</v>
@@ -2430,11 +2418,11 @@
         <v>(scénario personnel à définir)</v>
       </c>
       <c r="D32" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 2",'Lisez-moi'!$B$14)</f>
+        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 2",'Lisez-moi'!$B$13)</f>
         <v>Testeur 2</v>
       </c>
       <c r="E32" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
       <c r="F32" s="14"/>
@@ -2443,7 +2431,7 @@
     </row>
     <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B33" s="12" t="n">
         <v>13</v>
@@ -2453,11 +2441,11 @@
         <v>(scénario personnel à définir)</v>
       </c>
       <c r="D33" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 2",'Lisez-moi'!$B$14)</f>
+        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 2",'Lisez-moi'!$B$13)</f>
         <v>Testeur 2</v>
       </c>
       <c r="E33" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
       <c r="F33" s="14"/>
@@ -2466,7 +2454,7 @@
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B34" s="12" t="n">
         <v>14</v>
@@ -2476,11 +2464,11 @@
         <v>(scénario personnel à définir)</v>
       </c>
       <c r="D34" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 2",'Lisez-moi'!$B$14)</f>
+        <f aca="false">IF('Lisez-moi'!$B$13="","Testeur 2",'Lisez-moi'!$B$13)</f>
         <v>Testeur 2</v>
       </c>
       <c r="E34" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
       <c r="F34" s="14"/>
@@ -2489,7 +2477,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="str">
-        <f aca="false">"Testeur 3 : "&amp;IF('Lisez-moi'!B15="","(nom à inscrire dans Lisez-moi)",'Lisez-moi'!B15)</f>
+        <f aca="false">"Testeur 3 : "&amp;IF('Lisez-moi'!B14="","(nom à inscrire dans Lisez-moi)",'Lisez-moi'!B14)</f>
         <v>Testeur 3 : (nom à inscrire dans Lisez-moi)</v>
       </c>
       <c r="B35" s="13"/>
@@ -2502,7 +2490,7 @@
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B36" s="12" t="n">
         <v>1</v>
@@ -2512,11 +2500,11 @@
         <v>Première impression</v>
       </c>
       <c r="D36" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$15="","Testeur 3",'Lisez-moi'!$B$15)</f>
+        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 3",'Lisez-moi'!$B$14)</f>
         <v>Testeur 3</v>
       </c>
       <c r="E36" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$15&amp;" "&amp;'Lisez-moi'!$D$15)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
         <v/>
       </c>
       <c r="F36" s="14"/>
@@ -2525,7 +2513,7 @@
     </row>
     <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B37" s="12" t="n">
         <v>2</v>
@@ -2535,11 +2523,11 @@
         <v>Navigation par le menu</v>
       </c>
       <c r="D37" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$15="","Testeur 3",'Lisez-moi'!$B$15)</f>
+        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 3",'Lisez-moi'!$B$14)</f>
         <v>Testeur 3</v>
       </c>
       <c r="E37" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$15&amp;" "&amp;'Lisez-moi'!$D$15)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
         <v/>
       </c>
       <c r="F37" s="14"/>
@@ -2548,7 +2536,7 @@
     </row>
     <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B38" s="12" t="n">
         <v>3</v>
@@ -2558,11 +2546,11 @@
         <v>Liste des projets</v>
       </c>
       <c r="D38" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$15="","Testeur 3",'Lisez-moi'!$B$15)</f>
+        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 3",'Lisez-moi'!$B$14)</f>
         <v>Testeur 3</v>
       </c>
       <c r="E38" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$15&amp;" "&amp;'Lisez-moi'!$D$15)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
         <v/>
       </c>
       <c r="F38" s="14"/>
@@ -2571,7 +2559,7 @@
     </row>
     <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>4</v>
@@ -2581,11 +2569,11 @@
         <v>Détail d'un projet</v>
       </c>
       <c r="D39" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$15="","Testeur 3",'Lisez-moi'!$B$15)</f>
+        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 3",'Lisez-moi'!$B$14)</f>
         <v>Testeur 3</v>
       </c>
       <c r="E39" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$15&amp;" "&amp;'Lisez-moi'!$D$15)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
         <v/>
       </c>
       <c r="F39" s="14"/>
@@ -2594,7 +2582,7 @@
     </row>
     <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B40" s="12" t="n">
         <v>5</v>
@@ -2604,11 +2592,11 @@
         <v>Liens externes et contact</v>
       </c>
       <c r="D40" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$15="","Testeur 3",'Lisez-moi'!$B$15)</f>
+        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 3",'Lisez-moi'!$B$14)</f>
         <v>Testeur 3</v>
       </c>
       <c r="E40" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$15&amp;" "&amp;'Lisez-moi'!$D$15)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
         <v/>
       </c>
       <c r="F40" s="14"/>
@@ -2617,7 +2605,7 @@
     </row>
     <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B41" s="12" t="n">
         <v>6</v>
@@ -2627,11 +2615,11 @@
         <v>Version mobile</v>
       </c>
       <c r="D41" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$15="","Testeur 3",'Lisez-moi'!$B$15)</f>
+        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 3",'Lisez-moi'!$B$14)</f>
         <v>Testeur 3</v>
       </c>
       <c r="E41" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$15&amp;" "&amp;'Lisez-moi'!$D$15)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
         <v/>
       </c>
       <c r="F41" s="14"/>
@@ -2640,7 +2628,7 @@
     </row>
     <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B42" s="12" t="n">
         <v>7</v>
@@ -2650,11 +2638,11 @@
         <v>Navigation au clavier</v>
       </c>
       <c r="D42" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$15="","Testeur 3",'Lisez-moi'!$B$15)</f>
+        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 3",'Lisez-moi'!$B$14)</f>
         <v>Testeur 3</v>
       </c>
       <c r="E42" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$15&amp;" "&amp;'Lisez-moi'!$D$15)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
         <v/>
       </c>
       <c r="F42" s="14"/>
@@ -2663,7 +2651,7 @@
     </row>
     <row r="43" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B43" s="12" t="n">
         <v>8</v>
@@ -2673,11 +2661,11 @@
         <v>Contraste des textes</v>
       </c>
       <c r="D43" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$15="","Testeur 3",'Lisez-moi'!$B$15)</f>
+        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 3",'Lisez-moi'!$B$14)</f>
         <v>Testeur 3</v>
       </c>
       <c r="E43" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$15&amp;" "&amp;'Lisez-moi'!$D$15)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
         <v/>
       </c>
       <c r="F43" s="14"/>
@@ -2686,7 +2674,7 @@
     </row>
     <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B44" s="12" t="n">
         <v>9</v>
@@ -2696,11 +2684,11 @@
         <v>Structure et textes alternatifs</v>
       </c>
       <c r="D44" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$15="","Testeur 3",'Lisez-moi'!$B$15)</f>
+        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 3",'Lisez-moi'!$B$14)</f>
         <v>Testeur 3</v>
       </c>
       <c r="E44" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$15&amp;" "&amp;'Lisez-moi'!$D$15)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
         <v/>
       </c>
       <c r="F44" s="14"/>
@@ -2709,7 +2697,7 @@
     </row>
     <row r="45" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B45" s="12" t="n">
         <v>10</v>
@@ -2719,11 +2707,11 @@
         <v>Console et réseau</v>
       </c>
       <c r="D45" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$15="","Testeur 3",'Lisez-moi'!$B$15)</f>
+        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 3",'Lisez-moi'!$B$14)</f>
         <v>Testeur 3</v>
       </c>
       <c r="E45" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$15&amp;" "&amp;'Lisez-moi'!$D$15)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
         <v/>
       </c>
       <c r="F45" s="14"/>
@@ -2732,7 +2720,7 @@
     </row>
     <row r="46" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B46" s="12" t="n">
         <v>11</v>
@@ -2742,11 +2730,11 @@
         <v>Chargement sur connexion lente</v>
       </c>
       <c r="D46" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$15="","Testeur 3",'Lisez-moi'!$B$15)</f>
+        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 3",'Lisez-moi'!$B$14)</f>
         <v>Testeur 3</v>
       </c>
       <c r="E46" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$15&amp;" "&amp;'Lisez-moi'!$D$15)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
         <v/>
       </c>
       <c r="F46" s="14"/>
@@ -2755,7 +2743,7 @@
     </row>
     <row r="47" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B47" s="12" t="n">
         <v>12</v>
@@ -2765,11 +2753,11 @@
         <v>(scénario personnel à définir)</v>
       </c>
       <c r="D47" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$15="","Testeur 3",'Lisez-moi'!$B$15)</f>
+        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 3",'Lisez-moi'!$B$14)</f>
         <v>Testeur 3</v>
       </c>
       <c r="E47" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$15&amp;" "&amp;'Lisez-moi'!$D$15)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
         <v/>
       </c>
       <c r="F47" s="14"/>
@@ -2778,7 +2766,7 @@
     </row>
     <row r="48" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B48" s="12" t="n">
         <v>13</v>
@@ -2788,11 +2776,11 @@
         <v>(scénario personnel à définir)</v>
       </c>
       <c r="D48" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$15="","Testeur 3",'Lisez-moi'!$B$15)</f>
+        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 3",'Lisez-moi'!$B$14)</f>
         <v>Testeur 3</v>
       </c>
       <c r="E48" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$15&amp;" "&amp;'Lisez-moi'!$D$15)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
         <v/>
       </c>
       <c r="F48" s="14"/>
@@ -2801,7 +2789,7 @@
     </row>
     <row r="49" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B49" s="12" t="n">
         <v>14</v>
@@ -2811,11 +2799,11 @@
         <v>(scénario personnel à définir)</v>
       </c>
       <c r="D49" s="7" t="str">
-        <f aca="false">IF('Lisez-moi'!$B$15="","Testeur 3",'Lisez-moi'!$B$15)</f>
+        <f aca="false">IF('Lisez-moi'!$B$14="","Testeur 3",'Lisez-moi'!$B$14)</f>
         <v>Testeur 3</v>
       </c>
       <c r="E49" s="7" t="str">
-        <f aca="false">TRIM('Lisez-moi'!$C$15&amp;" "&amp;'Lisez-moi'!$D$15)</f>
+        <f aca="false">TRIM('Lisez-moi'!$C$14&amp;" "&amp;'Lisez-moi'!$D$14)</f>
         <v/>
       </c>
       <c r="F49" s="14"/>
@@ -2878,41 +2866,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="G4" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3749,164 +3737,164 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="11" t="s">
         <v>157</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>159</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>160</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>173</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="5"/>
@@ -3943,25 +3931,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B5" s="12" t="n">
         <f aca="false">COUNTA(Tests!A5:A49)-3</f>
@@ -3970,7 +3958,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B6" s="12" t="n">
         <f aca="false">COUNTIF(Tests!F5:F49,"Conforme")+COUNTIF(Tests!F5:F49,"Écart")</f>
@@ -3979,7 +3967,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B7" s="12" t="n">
         <f aca="false">COUNTIF(Tests!F5:F49,"Conforme")</f>
@@ -3988,7 +3976,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B8" s="12" t="n">
         <f aca="false">COUNTIF(Tests!F5:F49,"Écart")</f>
@@ -3997,7 +3985,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B9" s="12" t="n">
         <f aca="false">COUNTIFS(Tests!F5:F49,"Écart",Tests!H5:H49,"Bloquant")</f>
@@ -4006,7 +3994,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B10" s="12" t="n">
         <f aca="false">COUNTIFS(Tests!F5:F49,"Écart",Tests!H5:H49,"Majeur")</f>
@@ -4015,7 +4003,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B11" s="12" t="n">
         <f aca="false">COUNTIFS(Tests!F5:F49,"Écart",Tests!H5:H49,"Mineur")</f>
@@ -4024,7 +4012,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">B8-B9-B10-B11</f>
@@ -4033,7 +4021,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B13" s="12" t="n">
         <f aca="false">COUNTA(Correctifs!A5:A44)</f>
@@ -4042,7 +4030,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">COUNTIF(Correctifs!H5:H44,"Oui")</f>
@@ -4051,7 +4039,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">IF(B8=0,0,B14/B8)</f>
@@ -4060,7 +4048,7 @@
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/docs/582-511-web5/projets/portfolio/qa-gabarit-portfolio.xlsx
+++ b/docs/582-511-web5/projets/portfolio/qa-gabarit-portfolio.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="32160" yWindow="-6790" windowWidth="24690" windowHeight="20760" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lisez-moi" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
@@ -23,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -33,7 +34,31 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF002060"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
       <i val="1"/>
       <color rgb="FF595959"/>
       <sz val="10"/>
@@ -41,30 +66,6 @@
     <font>
       <name val="Arial"/>
       <charset val="1"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <i val="1"/>
-      <color rgb="FF595959"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <family val="2"/>
       <b val="1"/>
       <color rgb="FF002060"/>
@@ -72,10 +73,37 @@
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FF002060"/>
-      <sz val="16"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -86,24 +114,22 @@
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="1"/>
+      <family val="0"/>
       <b val="1"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="10"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <i val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -118,32 +144,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF002060"/>
+        <bgColor rgb="FF000080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="-0.25"/>
+        <bgColor rgb="FF993366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.25"/>
+        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
-        <bgColor rgb="FFFF6600"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
-        <bgColor rgb="FF000000"/>
+        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
   </fills>
@@ -194,6 +214,17 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
@@ -211,115 +242,207 @@
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="54">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
       <font>
         <name val="Arial"/>
         <charset val="1"/>
-        <color rgb="FF2E7D32"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFF2B47"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
         <charset val="1"/>
-        <b val="1"/>
-        <color rgb="FFFF2B47"/>
+        <family val="0"/>
+        <color rgb="FF2E7D32"/>
       </font>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -339,7 +462,7 @@
       <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF953735"/>
       <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
@@ -365,12 +488,12 @@
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFFC000"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFE46C0A"/>
       <rgbColor rgb="FF595959"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF002060"/>
       <rgbColor rgb="FF2E7D32"/>
       <rgbColor rgb="FF0A0A0A"/>
       <rgbColor rgb="FF333300"/>
@@ -378,55 +501,47 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -434,12 +549,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -468,7 +583,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -489,7 +604,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -540,7 +655,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -558,409 +673,406 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <tabColor rgb="FF0A0A0A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:F38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="4"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" style="26" min="1" max="1"/>
+    <col width="26" customWidth="1" style="26" min="2" max="2"/>
+    <col width="22" customWidth="1" style="26" min="3" max="4"/>
+    <col width="16" customWidth="1" style="26" min="5" max="5"/>
+    <col width="40" customWidth="1" style="26" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="21" customHeight="1" s="27">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Contrôle de la qualité du portfolio</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2" ht="14.25" customHeight="1" s="27">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Web 5 (582-511 MO) · Cellules jaunes = à remplir. Les autres se remplissent seules.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15.6" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="27">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Votre portfolio</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5" ht="14.25" customHeight="1" s="27">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Prénom et nom</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="26" t="n"/>
-      <c r="D5" s="27" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="34" t="n"/>
+    </row>
+    <row r="6" ht="14.25" customHeight="1" s="27">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Groupe (Lora ou Enric)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="26" t="n"/>
-      <c r="D6" s="27" t="n"/>
-    </row>
-    <row r="7" ht="26.4" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="B6" s="32" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="34" t="n"/>
+    </row>
+    <row r="7" ht="26.25" customHeight="1" s="27">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>Adresse du site publié en ligne (https://….github.io/…)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="26" t="n"/>
-      <c r="D7" s="27" t="n"/>
-    </row>
-    <row r="9" ht="15.6" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="B7" s="32" t="n"/>
+      <c r="C7" s="33" t="n"/>
+      <c r="D7" s="34" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="27">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>Les 3 testeurs : un environnement différent chacun</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+    <row r="10" ht="14.25" customHeight="1" s="27">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Testeur</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>Prénom et Nom</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Navigateur</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Appareil et largeur (ex. ordinateur, 1920 px)</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>Date du test</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="26.4" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="26.25" customHeight="1" s="27">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Testeur 1 (vous)</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="32" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Auto-test : vous comptez comme l'une des 3 personnes.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12" ht="14.25" customHeight="1" s="27">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Testeur 2 (camarade)</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="37" t="n"/>
+    </row>
+    <row r="13" ht="14.25" customHeight="1" s="27">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Testeur 3 (camarade)</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="8" t="n"/>
-    </row>
-    <row r="15" ht="15.6" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="32" t="n"/>
+      <c r="E13" s="32" t="n"/>
+      <c r="F13" s="37" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="27">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>Mode d'emploi</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="27.75" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="16" ht="27.75" customHeight="1" s="27">
+      <c r="A16" s="38" t="inlineStr">
         <is>
           <t>1. Remplissez les cellules jaunes ci-dessus. Ajoutez 2 ou 3 scénarios personnels dans l'onglet Scénarios (scénarios 12 à 14).</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="27.75" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="17" ht="27.75" customHeight="1" s="27">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>2. Les tests se font sur l'adresse de votre site, pendant que GitHub Pages publie encore la branche beta. Chaque testeur fait tous les scénarios, dans l'onglet Tests, dans son bloc.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="27.75" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="18" ht="27.75" customHeight="1" s="27">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>3. Pour chaque ligne : Résultat = Conforme ou Écart. Si Écart : décrivez ce que vous observez et choisissez une gravité.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="27.75" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
+    <row r="19" ht="27.75" customHeight="1" s="27">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>4. Une fois les 3 tests terminés seulement : l'auteur passe "GitHub Pages" sur la branche main, puis corrige sur main.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="27.75" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="20" ht="27.75" customHeight="1" s="27">
+      <c r="A20" s="38" t="inlineStr">
         <is>
           <t>5. Chaque écart corrigé va dans l'onglet Correctifs : le correctif, le commit, puis la validation (scénario refait en ligne, sur main).</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="27.75" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+    <row r="21" ht="27.75" customHeight="1" s="27">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>6. À la maison en devoir : l'onglet Autoévaluation, avec la grille critériée. L'onglet Synthèse se calcule seul.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15.6" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="27">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>Gravité</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="27.75" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="24" ht="27.75" customHeight="1" s="27">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>Bloquant</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="41" t="inlineStr">
         <is>
           <t>Empêche d'utiliser le site ou une fonction (cartes absentes, lien mort vers un projet, menu inutilisable sur mobile).</t>
         </is>
       </c>
-      <c r="C24" s="26" t="n"/>
-      <c r="D24" s="26" t="n"/>
-      <c r="E24" s="26" t="n"/>
-      <c r="F24" s="26" t="n"/>
-    </row>
-    <row r="25" ht="27.75" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="33" t="n"/>
+    </row>
+    <row r="25" ht="27.75" customHeight="1" s="27">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>Majeur</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="41" t="inlineStr">
         <is>
           <t>Nuit clairement à l'expérience (contraste insuffisant, focus invisible, image très lourde, texte qui déborde).</t>
         </is>
       </c>
-      <c r="C25" s="26" t="n"/>
-      <c r="D25" s="26" t="n"/>
-      <c r="E25" s="26" t="n"/>
-      <c r="F25" s="26" t="n"/>
-    </row>
-    <row r="26" ht="27.75" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="C25" s="33" t="n"/>
+      <c r="D25" s="33" t="n"/>
+      <c r="E25" s="33" t="n"/>
+      <c r="F25" s="33" t="n"/>
+    </row>
+    <row r="26" ht="27.75" customHeight="1" s="27">
+      <c r="A26" s="43" t="inlineStr">
         <is>
           <t>Mineur</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="41" t="inlineStr">
         <is>
           <t>Détail à améliorer (alignement, espacement, petite incohérence visuelle).</t>
         </is>
       </c>
-      <c r="C26" s="26" t="n"/>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="26" t="n"/>
-      <c r="F26" s="26" t="n"/>
-    </row>
-    <row r="28" ht="15.6" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="C26" s="33" t="n"/>
+      <c r="D26" s="33" t="n"/>
+      <c r="E26" s="33" t="n"/>
+      <c r="F26" s="33" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="27">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>Exemple de ligne bien remplie (Tests)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29" ht="15" customHeight="1" s="27">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>Scénario</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B29" s="44" t="inlineStr">
         <is>
           <t>7. Navigation au clavier</t>
         </is>
       </c>
-      <c r="C29" s="26" t="n"/>
-      <c r="D29" s="26" t="n"/>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="26" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="C29" s="33" t="n"/>
+      <c r="D29" s="33" t="n"/>
+      <c r="E29" s="33" t="n"/>
+      <c r="F29" s="33" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="27">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>Testeur</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B30" s="44" t="inlineStr">
         <is>
           <t>Testeur 2 (Firefox, ordinateur)</t>
         </is>
       </c>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="26" t="n"/>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="26" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="33" t="n"/>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="33" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="27">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>Résultat</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B31" s="44" t="inlineStr">
         <is>
           <t>Écart</t>
         </is>
       </c>
-      <c r="C31" s="26" t="n"/>
-      <c r="D31" s="26" t="n"/>
-      <c r="E31" s="26" t="n"/>
-      <c r="F31" s="26" t="n"/>
-    </row>
-    <row r="32" ht="27.75" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="C31" s="33" t="n"/>
+      <c r="D31" s="33" t="n"/>
+      <c r="E31" s="33" t="n"/>
+      <c r="F31" s="33" t="n"/>
+    </row>
+    <row r="32" ht="27.75" customHeight="1" s="27">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>Résultat observé</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B32" s="44" t="inlineStr">
         <is>
           <t>Sur l'accueil, le focus disparaît sur les cartes de projets : impossible de savoir quelle carte est sélectionnée. Échap ne ferme pas la modale.</t>
         </is>
       </c>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="26" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="C32" s="33" t="n"/>
+      <c r="D32" s="33" t="n"/>
+      <c r="E32" s="33" t="n"/>
+      <c r="F32" s="33" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="27">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>Gravité</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B33" s="44" t="inlineStr">
         <is>
           <t>Majeur</t>
         </is>
       </c>
-      <c r="C33" s="26" t="n"/>
-      <c r="D33" s="26" t="n"/>
-      <c r="E33" s="26" t="n"/>
-      <c r="F33" s="26" t="n"/>
-    </row>
-    <row r="35" ht="15.6" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="C33" s="33" t="n"/>
+      <c r="D33" s="33" t="n"/>
+      <c r="E33" s="33" t="n"/>
+      <c r="F33" s="33" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="27">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>Exemple de ligne bien remplie (Correctifs)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="27.75" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="36" ht="27.75" customHeight="1" s="27">
+      <c r="A36" s="31" t="inlineStr">
         <is>
           <t>Correctif</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
+      <c r="B36" s="44" t="inlineStr">
         <is>
           <t>Ajout d'un style :focus-visible sur .project-card__button; la modale utilise maintenant &lt;dialog&gt; avec showModal(), qui gère Échap.</t>
         </is>
       </c>
-      <c r="C36" s="26" t="n"/>
-      <c r="D36" s="26" t="n"/>
-      <c r="E36" s="26" t="n"/>
-      <c r="F36" s="26" t="n"/>
-    </row>
-    <row r="37" ht="27.75" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="33" t="n"/>
+      <c r="E36" s="33" t="n"/>
+      <c r="F36" s="33" t="n"/>
+    </row>
+    <row r="37" ht="27.75" customHeight="1" s="27">
+      <c r="A37" s="31" t="inlineStr">
         <is>
           <t>Commit</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
+      <c r="B37" s="44" t="inlineStr">
         <is>
           <t>T-21 : focus visible et fermeture de la modale au clavier</t>
         </is>
       </c>
-      <c r="C37" s="26" t="n"/>
-      <c r="D37" s="26" t="n"/>
-      <c r="E37" s="26" t="n"/>
-      <c r="F37" s="26" t="n"/>
-    </row>
-    <row r="38" ht="27.75" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="C37" s="33" t="n"/>
+      <c r="D37" s="33" t="n"/>
+      <c r="E37" s="33" t="n"/>
+      <c r="F37" s="33" t="n"/>
+    </row>
+    <row r="38" ht="27.75" customHeight="1" s="27">
+      <c r="A38" s="31" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="B38" s="44" t="inlineStr">
         <is>
           <t>Scénario 7 refait le 6 oct. en ligne (Pages sur main), Firefox : focus visible partout, Échap ferme la modale. Validé : Oui</t>
         </is>
       </c>
-      <c r="C38" s="26" t="n"/>
-      <c r="D38" s="26" t="n"/>
-      <c r="E38" s="26" t="n"/>
-      <c r="F38" s="26" t="n"/>
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -985,1534 +1097,1536 @@
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B26:F26"/>
   </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <tabColor rgb="FF0A0A0A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" style="26" min="1" max="1"/>
+    <col width="34" customWidth="1" style="26" min="2" max="2"/>
+    <col width="58" customWidth="1" style="26" min="3" max="3"/>
+    <col width="42" customWidth="1" style="26" min="4" max="4"/>
+    <col width="26" customWidth="1" style="26" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="21" customHeight="1" s="27">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Scénarios de test</t>
         </is>
       </c>
-      <c r="B1" s="19" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="B1" s="45" t="n"/>
+    </row>
+    <row r="2" ht="14.25" customHeight="1" s="27">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>1 à 11 : tronc commun, pour tout le monde. 12 à 14 : vos scénarios personnels (cellules jaunes).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="27">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>Scénario</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>Comment faire</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="46" t="inlineStr">
         <is>
           <t>Résultat attendu</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="46" t="inlineStr">
         <is>
           <t>Lien avec la grille</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="57.75" customHeight="1">
-      <c r="A5" s="9" t="n">
+    <row r="5" ht="57.75" customHeight="1" s="27">
+      <c r="A5" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Première impression</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>Regardez l'accueil 5 secondes, puis détournez les yeux. Dites qui est la personne et ce qu'elle fait.</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Réponse juste, sans avoir cherché ni fait défiler.</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>C1 cohérence visuelle; C3 lisibilité</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="57.75" customHeight="1">
-      <c r="A6" s="9" t="n">
+    <row r="6" ht="57.75" customHeight="1" s="27">
+      <c r="A6" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Navigation par le menu</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>À partir du menu, atteignez chaque section ou page, puis revenez à l'accueil.</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Chaque lien mène au bon endroit. Aucun lien mort, aucune page vide.</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>C2 navigation</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="57.75" customHeight="1">
-      <c r="A7" s="9" t="n">
+    <row r="7" ht="57.75" customHeight="1" s="27">
+      <c r="A7" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>Liste des projets</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>Parcourez la section des projets.</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Toutes les cartes s'affichent, chacune avec son image et son titre. Aucune image cassée.</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>C2 chargement des données</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="57.75" customHeight="1">
-      <c r="A8" s="9" t="n">
+    <row r="8" ht="57.75" customHeight="1" s="27">
+      <c r="A8" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>Détail d'un projet</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>Ouvrez le détail de 2 projets différents, puis revenez ou fermez.</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Le contenu correspond au projet cliqué. Le retour ou la fermeture fonctionne.</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>C2 éléments interactifs</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="57.75" customHeight="1">
-      <c r="A9" s="9" t="n">
+    <row r="9" ht="57.75" customHeight="1" s="27">
+      <c r="A9" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>Liens externes et contact</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>Cliquez sur chaque lien externe (réseaux, vidéo, CV, courriel...).</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Chaque lien mène au bon endroit. Les liens externes ne vous font pas perdre le portfolio.</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>C2 navigation</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="57.75" customHeight="1">
-      <c r="A10" s="9" t="n">
+    <row r="10" ht="57.75" customHeight="1" s="27">
+      <c r="A10" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>Version mobile</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>Sur un téléphone (ou le mode appareil de l'inspecteur, 375 px), refaites les scénarios 2 à 4.</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>Rien ne déborde horizontalement. Le menu est utilisable. Les textes sont lisibles sans zoomer.</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>C2 responsive</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="57.75" customHeight="1">
-      <c r="A11" s="9" t="n">
+    <row r="11" ht="57.75" customHeight="1" s="27">
+      <c r="A11" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Navigation au clavier</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>Sans toucher à la souris, refaites les scénarios 2 à 4 : Tab, Maj+Tab, Entrée, Espace, Échap. (Mac/Safari : voir la page Accessibilité.)</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>Tout est atteignable. On voit toujours où est le focus. L'ordre est logique. Échap ferme une modale.</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>C2 WCAG : clavier</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="57.75" customHeight="1">
-      <c r="A12" s="9" t="n">
+    <row r="12" ht="57.75" customHeight="1" s="27">
+      <c r="A12" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>Contraste des textes</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>Inspecteur : cliquez sur la couleur d'un texte (Styles) pour voir le ratio. Testez le texte courant, les liens, les boutons, le texte sur image.</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>Ratio AA respecté : 4,5:1 pour le texte courant, 3:1 pour le gros texte (24 px, ou 18,5 px en gras).</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="37" t="inlineStr">
         <is>
           <t>C2 WCAG : contraste</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="57.75" customHeight="1">
-      <c r="A13" s="9" t="n">
+    <row r="13" ht="57.75" customHeight="1" s="27">
+      <c r="A13" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>Structure et textes alternatifs</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Lancez l'extension WAVE sur l'accueil et sur le détail d'un projet. Notez les erreurs (rouge) et les alertes de contraste.</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>Collez l'adresse du site dans wave.webaim.org (en multipages, aussi celle d'un détail de projet). Notez les erreurs (rouge) et les erreurs de contraste.</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Aucune erreur WAVE. Images informatives avec un alt descriptif, images décoratives avec alt="". Un seul h1 par page.</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>C2 WCAG : sémantique et alt</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="57.75" customHeight="1">
-      <c r="A14" s="9" t="n">
+    <row r="14" ht="57.75" customHeight="1" s="27">
+      <c r="A14" s="47" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>Console et réseau</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>Ouvrez l'inspecteur (F12), onglets Console et Réseau, puis refaites les scénarios 2 à 4.</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Aucune erreur rouge dans la console. Aucune ressource en 404 dans Réseau.</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>C2 sans erreur</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="57.75" customHeight="1">
-      <c r="A15" s="9" t="n">
+    <row r="15" ht="57.75" customHeight="1" s="27">
+      <c r="A15" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>Chargement sur connexion lente</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>Réseau : cochez Désactiver le cache, choisissez « Slow 4G », puis rechargez l'accueil. Notez le poids total (bas de l'onglet Réseau).</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Le contenu principal apparaît rapidement. Aucune image ne pèse plus de quelques centaines de Ko.</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>C1 médias; C2 chargement perçu</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="57.75" customHeight="1">
-      <c r="A16" s="9" t="n">
+    <row r="16" ht="57.75" customHeight="1" s="27">
+      <c r="A16" s="47" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="B16" s="32" t="n"/>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="32" t="n"/>
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>C3 exhaustivité</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="57.75" customHeight="1">
-      <c r="A17" s="9" t="n">
+    <row r="17" ht="57.75" customHeight="1" s="27">
+      <c r="A17" s="47" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="B17" s="32" t="n"/>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="32" t="n"/>
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>C3 exhaustivité</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="57.75" customHeight="1">
-      <c r="A18" s="9" t="n">
+    <row r="18" ht="57.75" customHeight="1" s="27">
+      <c r="A18" s="47" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="B18" s="32" t="n"/>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="37" t="inlineStr">
         <is>
           <t>C3 exhaustivité</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <tabColor rgb="FFFF2B47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:H49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="54" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" style="26" min="1" max="1"/>
+    <col width="5" customWidth="1" style="26" min="2" max="2"/>
+    <col width="28" customWidth="1" style="26" min="3" max="3"/>
+    <col width="22" customWidth="1" style="26" min="4" max="4"/>
+    <col width="24" customWidth="1" style="26" min="5" max="5"/>
+    <col width="12" customWidth="1" style="26" min="6" max="6"/>
+    <col width="54" customWidth="1" style="26" min="7" max="7"/>
+    <col width="12" customWidth="1" style="26" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="21" customHeight="1" s="27">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Résultats des tests</t>
         </is>
       </c>
-      <c r="C1" s="19" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="C1" s="45" t="n"/>
+    </row>
+    <row r="2" ht="14.25" customHeight="1" s="27">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Tests faits pendant que le site publie la branche beta. Chaque testeur remplit son bloc. Cellules jaunes = à remplir.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="27">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>Scénario</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>Testeur</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="48" t="inlineStr">
         <is>
           <t>Environnement</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="48" t="inlineStr">
         <is>
           <t>Résultat</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="G4" s="48" t="inlineStr">
         <is>
           <t>Résultat observé (si écart)</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="48" t="inlineStr">
         <is>
           <t>Gravité</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="20">
+    <row r="5" ht="14.25" customHeight="1" s="27">
+      <c r="A5" s="49">
         <f>"Testeur 1 : "&amp;IF('Lisez-moi'!B11="","(nom à inscrire dans Lisez-moi)",'Lisez-moi'!B11)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+    <row r="6" ht="31.5" customHeight="1" s="27">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>T-01</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,1)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,1))</f>
         <v/>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="37">
         <f>IF('Lisez-moi'!$B$11="","Testeur 1",'Lisez-moi'!$B$11)</f>
         <v/>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="37">
         <f>TRIM('Lisez-moi'!$C$11&amp;" "&amp;'Lisez-moi'!$D$11)</f>
         <v/>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="10" t="n"/>
-    </row>
-    <row r="7" ht="31.5" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="F6" s="50" t="n"/>
+      <c r="G6" s="32" t="n"/>
+      <c r="H6" s="50" t="n"/>
+    </row>
+    <row r="7" ht="31.5" customHeight="1" s="27">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>T-02</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,2)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,2))</f>
         <v/>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="37">
         <f>IF('Lisez-moi'!$B$11="","Testeur 1",'Lisez-moi'!$B$11)</f>
         <v/>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="37">
         <f>TRIM('Lisez-moi'!$C$11&amp;" "&amp;'Lisez-moi'!$D$11)</f>
         <v/>
       </c>
-      <c r="F7" s="10" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="10" t="n"/>
-    </row>
-    <row r="8" ht="31.5" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="F7" s="50" t="n"/>
+      <c r="G7" s="32" t="n"/>
+      <c r="H7" s="50" t="n"/>
+    </row>
+    <row r="8" ht="31.5" customHeight="1" s="27">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>T-03</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,3)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,3))</f>
         <v/>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="37">
         <f>IF('Lisez-moi'!$B$11="","Testeur 1",'Lisez-moi'!$B$11)</f>
         <v/>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="37">
         <f>TRIM('Lisez-moi'!$C$11&amp;" "&amp;'Lisez-moi'!$D$11)</f>
         <v/>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="10" t="n"/>
-    </row>
-    <row r="9" ht="31.5" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="F8" s="50" t="n"/>
+      <c r="G8" s="32" t="n"/>
+      <c r="H8" s="50" t="n"/>
+    </row>
+    <row r="9" ht="31.5" customHeight="1" s="27">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,4)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,4))</f>
         <v/>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="37">
         <f>IF('Lisez-moi'!$B$11="","Testeur 1",'Lisez-moi'!$B$11)</f>
         <v/>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="37">
         <f>TRIM('Lisez-moi'!$C$11&amp;" "&amp;'Lisez-moi'!$D$11)</f>
         <v/>
       </c>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="10" t="n"/>
-    </row>
-    <row r="10" ht="31.5" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="F9" s="50" t="n"/>
+      <c r="G9" s="32" t="n"/>
+      <c r="H9" s="50" t="n"/>
+    </row>
+    <row r="10" ht="31.5" customHeight="1" s="27">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>T-05</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,5)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,5))</f>
         <v/>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="37">
         <f>IF('Lisez-moi'!$B$11="","Testeur 1",'Lisez-moi'!$B$11)</f>
         <v/>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="37">
         <f>TRIM('Lisez-moi'!$C$11&amp;" "&amp;'Lisez-moi'!$D$11)</f>
         <v/>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="10" t="n"/>
-    </row>
-    <row r="11" ht="31.5" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="F10" s="50" t="n"/>
+      <c r="G10" s="32" t="n"/>
+      <c r="H10" s="50" t="n"/>
+    </row>
+    <row r="11" ht="31.5" customHeight="1" s="27">
+      <c r="A11" s="47" t="inlineStr">
         <is>
           <t>T-06</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,6)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,6))</f>
         <v/>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="37">
         <f>IF('Lisez-moi'!$B$11="","Testeur 1",'Lisez-moi'!$B$11)</f>
         <v/>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="37">
         <f>TRIM('Lisez-moi'!$C$11&amp;" "&amp;'Lisez-moi'!$D$11)</f>
         <v/>
       </c>
-      <c r="F11" s="10" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="10" t="n"/>
-    </row>
-    <row r="12" ht="31.5" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="F11" s="50" t="n"/>
+      <c r="G11" s="32" t="n"/>
+      <c r="H11" s="50" t="n"/>
+    </row>
+    <row r="12" ht="31.5" customHeight="1" s="27">
+      <c r="A12" s="47" t="inlineStr">
         <is>
           <t>T-07</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,7)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,7))</f>
         <v/>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="37">
         <f>IF('Lisez-moi'!$B$11="","Testeur 1",'Lisez-moi'!$B$11)</f>
         <v/>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="37">
         <f>TRIM('Lisez-moi'!$C$11&amp;" "&amp;'Lisez-moi'!$D$11)</f>
         <v/>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="10" t="n"/>
-    </row>
-    <row r="13" ht="31.5" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="F12" s="50" t="n"/>
+      <c r="G12" s="32" t="n"/>
+      <c r="H12" s="50" t="n"/>
+    </row>
+    <row r="13" ht="31.5" customHeight="1" s="27">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>T-08</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,8)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,8))</f>
         <v/>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="37">
         <f>IF('Lisez-moi'!$B$11="","Testeur 1",'Lisez-moi'!$B$11)</f>
         <v/>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="37">
         <f>TRIM('Lisez-moi'!$C$11&amp;" "&amp;'Lisez-moi'!$D$11)</f>
         <v/>
       </c>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="31.5" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="F13" s="50" t="n"/>
+      <c r="G13" s="32" t="n"/>
+      <c r="H13" s="50" t="n"/>
+    </row>
+    <row r="14" ht="31.5" customHeight="1" s="27">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>T-09</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,9)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,9))</f>
         <v/>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="37">
         <f>IF('Lisez-moi'!$B$11="","Testeur 1",'Lisez-moi'!$B$11)</f>
         <v/>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="37">
         <f>TRIM('Lisez-moi'!$C$11&amp;" "&amp;'Lisez-moi'!$D$11)</f>
         <v/>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="10" t="n"/>
-    </row>
-    <row r="15" ht="31.5" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="F14" s="50" t="n"/>
+      <c r="G14" s="32" t="n"/>
+      <c r="H14" s="50" t="n"/>
+    </row>
+    <row r="15" ht="31.5" customHeight="1" s="27">
+      <c r="A15" s="47" t="inlineStr">
         <is>
           <t>T-10</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="47" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,10)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,10))</f>
         <v/>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="37">
         <f>IF('Lisez-moi'!$B$11="","Testeur 1",'Lisez-moi'!$B$11)</f>
         <v/>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="37">
         <f>TRIM('Lisez-moi'!$C$11&amp;" "&amp;'Lisez-moi'!$D$11)</f>
         <v/>
       </c>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="10" t="n"/>
-    </row>
-    <row r="16" ht="31.5" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="F15" s="50" t="n"/>
+      <c r="G15" s="32" t="n"/>
+      <c r="H15" s="50" t="n"/>
+    </row>
+    <row r="16" ht="31.5" customHeight="1" s="27">
+      <c r="A16" s="47" t="inlineStr">
         <is>
           <t>T-11</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,11)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,11))</f>
         <v/>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="37">
         <f>IF('Lisez-moi'!$B$11="","Testeur 1",'Lisez-moi'!$B$11)</f>
         <v/>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="37">
         <f>TRIM('Lisez-moi'!$C$11&amp;" "&amp;'Lisez-moi'!$D$11)</f>
         <v/>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="31.5" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="F16" s="50" t="n"/>
+      <c r="G16" s="32" t="n"/>
+      <c r="H16" s="50" t="n"/>
+    </row>
+    <row r="17" ht="31.5" customHeight="1" s="27">
+      <c r="A17" s="47" t="inlineStr">
         <is>
           <t>T-12</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="47" t="n">
         <v>12</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,12)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,12))</f>
         <v/>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="37">
         <f>IF('Lisez-moi'!$B$11="","Testeur 1",'Lisez-moi'!$B$11)</f>
         <v/>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="37">
         <f>TRIM('Lisez-moi'!$C$11&amp;" "&amp;'Lisez-moi'!$D$11)</f>
         <v/>
       </c>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="31.5" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="F17" s="50" t="n"/>
+      <c r="G17" s="32" t="n"/>
+      <c r="H17" s="50" t="n"/>
+    </row>
+    <row r="18" ht="31.5" customHeight="1" s="27">
+      <c r="A18" s="47" t="inlineStr">
         <is>
           <t>T-13</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="47" t="n">
         <v>13</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,13)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,13))</f>
         <v/>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="37">
         <f>IF('Lisez-moi'!$B$11="","Testeur 1",'Lisez-moi'!$B$11)</f>
         <v/>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="37">
         <f>TRIM('Lisez-moi'!$C$11&amp;" "&amp;'Lisez-moi'!$D$11)</f>
         <v/>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="10" t="n"/>
-    </row>
-    <row r="19" ht="31.5" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="F18" s="50" t="n"/>
+      <c r="G18" s="32" t="n"/>
+      <c r="H18" s="50" t="n"/>
+    </row>
+    <row r="19" ht="31.5" customHeight="1" s="27">
+      <c r="A19" s="47" t="inlineStr">
         <is>
           <t>T-14</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" s="47" t="n">
         <v>14</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,14)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,14))</f>
         <v/>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="37">
         <f>IF('Lisez-moi'!$B$11="","Testeur 1",'Lisez-moi'!$B$11)</f>
         <v/>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="37">
         <f>TRIM('Lisez-moi'!$C$11&amp;" "&amp;'Lisez-moi'!$D$11)</f>
         <v/>
       </c>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="10" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="20">
+      <c r="F19" s="50" t="n"/>
+      <c r="G19" s="32" t="n"/>
+      <c r="H19" s="50" t="n"/>
+    </row>
+    <row r="20" ht="14.25" customHeight="1" s="27">
+      <c r="A20" s="49">
         <f>"Testeur 2 : "&amp;IF('Lisez-moi'!B12="","(nom à inscrire dans Lisez-moi)",'Lisez-moi'!B12)</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="31.5" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="21" ht="31.5" customHeight="1" s="27">
+      <c r="A21" s="47" t="inlineStr">
         <is>
           <t>T-15</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B21" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,1)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,1))</f>
         <v/>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="37">
         <f>IF('Lisez-moi'!$B$12="","Testeur 2",'Lisez-moi'!$B$12)</f>
         <v/>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="37">
         <f>TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="31.5" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="F21" s="50" t="n"/>
+      <c r="G21" s="32" t="n"/>
+      <c r="H21" s="50" t="n"/>
+    </row>
+    <row r="22" ht="31.5" customHeight="1" s="27">
+      <c r="A22" s="47" t="inlineStr">
         <is>
           <t>T-16</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,2)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,2))</f>
         <v/>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="37">
         <f>IF('Lisez-moi'!$B$12="","Testeur 2",'Lisez-moi'!$B$12)</f>
         <v/>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="37">
         <f>TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="31.5" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="F22" s="50" t="n"/>
+      <c r="G22" s="32" t="n"/>
+      <c r="H22" s="50" t="n"/>
+    </row>
+    <row r="23" ht="31.5" customHeight="1" s="27">
+      <c r="A23" s="47" t="inlineStr">
         <is>
           <t>T-17</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B23" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,3)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,3))</f>
         <v/>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="37">
         <f>IF('Lisez-moi'!$B$12="","Testeur 2",'Lisez-moi'!$B$12)</f>
         <v/>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="37">
         <f>TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="31.5" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="F23" s="50" t="n"/>
+      <c r="G23" s="32" t="n"/>
+      <c r="H23" s="50" t="n"/>
+    </row>
+    <row r="24" ht="31.5" customHeight="1" s="27">
+      <c r="A24" s="47" t="inlineStr">
         <is>
           <t>T-18</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,4)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,4))</f>
         <v/>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="37">
         <f>IF('Lisez-moi'!$B$12="","Testeur 2",'Lisez-moi'!$B$12)</f>
         <v/>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="37">
         <f>TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="31.5" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="F24" s="50" t="n"/>
+      <c r="G24" s="32" t="n"/>
+      <c r="H24" s="50" t="n"/>
+    </row>
+    <row r="25" ht="31.5" customHeight="1" s="27">
+      <c r="A25" s="47" t="inlineStr">
         <is>
           <t>T-19</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B25" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,5)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,5))</f>
         <v/>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="37">
         <f>IF('Lisez-moi'!$B$12="","Testeur 2",'Lisez-moi'!$B$12)</f>
         <v/>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="37">
         <f>TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="31.5" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="F25" s="50" t="n"/>
+      <c r="G25" s="32" t="n"/>
+      <c r="H25" s="50" t="n"/>
+    </row>
+    <row r="26" ht="31.5" customHeight="1" s="27">
+      <c r="A26" s="47" t="inlineStr">
         <is>
           <t>T-20</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,6)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,6))</f>
         <v/>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="37">
         <f>IF('Lisez-moi'!$B$12="","Testeur 2",'Lisez-moi'!$B$12)</f>
         <v/>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="37">
         <f>TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="31.5" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="F26" s="50" t="n"/>
+      <c r="G26" s="32" t="n"/>
+      <c r="H26" s="50" t="n"/>
+    </row>
+    <row r="27" ht="31.5" customHeight="1" s="27">
+      <c r="A27" s="47" t="inlineStr">
         <is>
           <t>T-21</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
+      <c r="B27" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,7)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,7))</f>
         <v/>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="37">
         <f>IF('Lisez-moi'!$B$12="","Testeur 2",'Lisez-moi'!$B$12)</f>
         <v/>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="37">
         <f>TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="10" t="n"/>
-    </row>
-    <row r="28" ht="31.5" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="F27" s="50" t="n"/>
+      <c r="G27" s="32" t="n"/>
+      <c r="H27" s="50" t="n"/>
+    </row>
+    <row r="28" ht="31.5" customHeight="1" s="27">
+      <c r="A28" s="47" t="inlineStr">
         <is>
           <t>T-22</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B28" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,8)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,8))</f>
         <v/>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="37">
         <f>IF('Lisez-moi'!$B$12="","Testeur 2",'Lisez-moi'!$B$12)</f>
         <v/>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="37">
         <f>TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="10" t="n"/>
-    </row>
-    <row r="29" ht="31.5" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="F28" s="50" t="n"/>
+      <c r="G28" s="32" t="n"/>
+      <c r="H28" s="50" t="n"/>
+    </row>
+    <row r="29" ht="31.5" customHeight="1" s="27">
+      <c r="A29" s="47" t="inlineStr">
         <is>
           <t>T-23</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n">
+      <c r="B29" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,9)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,9))</f>
         <v/>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="37">
         <f>IF('Lisez-moi'!$B$12="","Testeur 2",'Lisez-moi'!$B$12)</f>
         <v/>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="37">
         <f>TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="10" t="n"/>
-    </row>
-    <row r="30" ht="31.5" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="F29" s="50" t="n"/>
+      <c r="G29" s="32" t="n"/>
+      <c r="H29" s="50" t="n"/>
+    </row>
+    <row r="30" ht="31.5" customHeight="1" s="27">
+      <c r="A30" s="47" t="inlineStr">
         <is>
           <t>T-24</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B30" s="47" t="n">
         <v>10</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,10)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,10))</f>
         <v/>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="37">
         <f>IF('Lisez-moi'!$B$12="","Testeur 2",'Lisez-moi'!$B$12)</f>
         <v/>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="37">
         <f>TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="10" t="n"/>
-    </row>
-    <row r="31" ht="31.5" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="F30" s="50" t="n"/>
+      <c r="G30" s="32" t="n"/>
+      <c r="H30" s="50" t="n"/>
+    </row>
+    <row r="31" ht="31.5" customHeight="1" s="27">
+      <c r="A31" s="47" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n">
+      <c r="B31" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,11)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,11))</f>
         <v/>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="37">
         <f>IF('Lisez-moi'!$B$12="","Testeur 2",'Lisez-moi'!$B$12)</f>
         <v/>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="37">
         <f>TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="31.5" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="F31" s="50" t="n"/>
+      <c r="G31" s="32" t="n"/>
+      <c r="H31" s="50" t="n"/>
+    </row>
+    <row r="32" ht="31.5" customHeight="1" s="27">
+      <c r="A32" s="47" t="inlineStr">
         <is>
           <t>T-26</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B32" s="47" t="n">
         <v>12</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,12)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,12))</f>
         <v/>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="37">
         <f>IF('Lisez-moi'!$B$12="","Testeur 2",'Lisez-moi'!$B$12)</f>
         <v/>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="37">
         <f>TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="10" t="n"/>
-    </row>
-    <row r="33" ht="31.5" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="F32" s="50" t="n"/>
+      <c r="G32" s="32" t="n"/>
+      <c r="H32" s="50" t="n"/>
+    </row>
+    <row r="33" ht="31.5" customHeight="1" s="27">
+      <c r="A33" s="47" t="inlineStr">
         <is>
           <t>T-27</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n">
+      <c r="B33" s="47" t="n">
         <v>13</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,13)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,13))</f>
         <v/>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="37">
         <f>IF('Lisez-moi'!$B$12="","Testeur 2",'Lisez-moi'!$B$12)</f>
         <v/>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="37">
         <f>TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="10" t="n"/>
-    </row>
-    <row r="34" ht="31.5" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="F33" s="50" t="n"/>
+      <c r="G33" s="32" t="n"/>
+      <c r="H33" s="50" t="n"/>
+    </row>
+    <row r="34" ht="31.5" customHeight="1" s="27">
+      <c r="A34" s="47" t="inlineStr">
         <is>
           <t>T-28</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n">
+      <c r="B34" s="47" t="n">
         <v>14</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,14)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,14))</f>
         <v/>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="37">
         <f>IF('Lisez-moi'!$B$12="","Testeur 2",'Lisez-moi'!$B$12)</f>
         <v/>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="37">
         <f>TRIM('Lisez-moi'!$C$12&amp;" "&amp;'Lisez-moi'!$D$12)</f>
         <v/>
       </c>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="10" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="20">
+      <c r="F34" s="50" t="n"/>
+      <c r="G34" s="32" t="n"/>
+      <c r="H34" s="50" t="n"/>
+    </row>
+    <row r="35" ht="14.25" customHeight="1" s="27">
+      <c r="A35" s="49">
         <f>"Testeur 3 : "&amp;IF('Lisez-moi'!B13="","(nom à inscrire dans Lisez-moi)",'Lisez-moi'!B13)</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="31.5" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="36" ht="31.5" customHeight="1" s="27">
+      <c r="A36" s="47" t="inlineStr">
         <is>
           <t>T-29</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n">
+      <c r="B36" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,1)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,1))</f>
         <v/>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="37">
         <f>IF('Lisez-moi'!$B$13="","Testeur 3",'Lisez-moi'!$B$13)</f>
         <v/>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="37">
         <f>TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="10" t="n"/>
-    </row>
-    <row r="37" ht="31.5" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="F36" s="50" t="n"/>
+      <c r="G36" s="32" t="n"/>
+      <c r="H36" s="50" t="n"/>
+    </row>
+    <row r="37" ht="31.5" customHeight="1" s="27">
+      <c r="A37" s="47" t="inlineStr">
         <is>
           <t>T-30</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n">
+      <c r="B37" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,2)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,2))</f>
         <v/>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="37">
         <f>IF('Lisez-moi'!$B$13="","Testeur 3",'Lisez-moi'!$B$13)</f>
         <v/>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="37">
         <f>TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="10" t="n"/>
-    </row>
-    <row r="38" ht="31.5" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="F37" s="50" t="n"/>
+      <c r="G37" s="32" t="n"/>
+      <c r="H37" s="50" t="n"/>
+    </row>
+    <row r="38" ht="31.5" customHeight="1" s="27">
+      <c r="A38" s="47" t="inlineStr">
         <is>
           <t>T-31</t>
         </is>
       </c>
-      <c r="B38" s="9" t="n">
+      <c r="B38" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,3)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,3))</f>
         <v/>
       </c>
-      <c r="D38" s="8">
+      <c r="D38" s="37">
         <f>IF('Lisez-moi'!$B$13="","Testeur 3",'Lisez-moi'!$B$13)</f>
         <v/>
       </c>
-      <c r="E38" s="8">
+      <c r="E38" s="37">
         <f>TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
-      <c r="F38" s="10" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="10" t="n"/>
-    </row>
-    <row r="39" ht="31.5" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="F38" s="50" t="n"/>
+      <c r="G38" s="32" t="n"/>
+      <c r="H38" s="50" t="n"/>
+    </row>
+    <row r="39" ht="31.5" customHeight="1" s="27">
+      <c r="A39" s="47" t="inlineStr">
         <is>
           <t>T-32</t>
         </is>
       </c>
-      <c r="B39" s="9" t="n">
+      <c r="B39" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="8">
+      <c r="C39" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,4)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,4))</f>
         <v/>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="37">
         <f>IF('Lisez-moi'!$B$13="","Testeur 3",'Lisez-moi'!$B$13)</f>
         <v/>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="37">
         <f>TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
-      <c r="F39" s="10" t="n"/>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="10" t="n"/>
-    </row>
-    <row r="40" ht="31.5" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="F39" s="50" t="n"/>
+      <c r="G39" s="32" t="n"/>
+      <c r="H39" s="50" t="n"/>
+    </row>
+    <row r="40" ht="31.5" customHeight="1" s="27">
+      <c r="A40" s="47" t="inlineStr">
         <is>
           <t>T-33</t>
         </is>
       </c>
-      <c r="B40" s="9" t="n">
+      <c r="B40" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="C40" s="8">
+      <c r="C40" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,5)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,5))</f>
         <v/>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="37">
         <f>IF('Lisez-moi'!$B$13="","Testeur 3",'Lisez-moi'!$B$13)</f>
         <v/>
       </c>
-      <c r="E40" s="8">
+      <c r="E40" s="37">
         <f>TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="10" t="n"/>
-    </row>
-    <row r="41" ht="31.5" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="F40" s="50" t="n"/>
+      <c r="G40" s="32" t="n"/>
+      <c r="H40" s="50" t="n"/>
+    </row>
+    <row r="41" ht="31.5" customHeight="1" s="27">
+      <c r="A41" s="47" t="inlineStr">
         <is>
           <t>T-34</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n">
+      <c r="B41" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="C41" s="8">
+      <c r="C41" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,6)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,6))</f>
         <v/>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="37">
         <f>IF('Lisez-moi'!$B$13="","Testeur 3",'Lisez-moi'!$B$13)</f>
         <v/>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="37">
         <f>TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
-      <c r="F41" s="10" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="10" t="n"/>
-    </row>
-    <row r="42" ht="31.5" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="F41" s="50" t="n"/>
+      <c r="G41" s="32" t="n"/>
+      <c r="H41" s="50" t="n"/>
+    </row>
+    <row r="42" ht="31.5" customHeight="1" s="27">
+      <c r="A42" s="47" t="inlineStr">
         <is>
           <t>T-35</t>
         </is>
       </c>
-      <c r="B42" s="9" t="n">
+      <c r="B42" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="C42" s="8">
+      <c r="C42" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,7)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,7))</f>
         <v/>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="37">
         <f>IF('Lisez-moi'!$B$13="","Testeur 3",'Lisez-moi'!$B$13)</f>
         <v/>
       </c>
-      <c r="E42" s="8">
+      <c r="E42" s="37">
         <f>TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="7" t="n"/>
-      <c r="H42" s="10" t="n"/>
-    </row>
-    <row r="43" ht="31.5" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="F42" s="50" t="n"/>
+      <c r="G42" s="32" t="n"/>
+      <c r="H42" s="50" t="n"/>
+    </row>
+    <row r="43" ht="31.5" customHeight="1" s="27">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>T-36</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n">
+      <c r="B43" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="C43" s="8">
+      <c r="C43" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,8)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,8))</f>
         <v/>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="37">
         <f>IF('Lisez-moi'!$B$13="","Testeur 3",'Lisez-moi'!$B$13)</f>
         <v/>
       </c>
-      <c r="E43" s="8">
+      <c r="E43" s="37">
         <f>TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
-      <c r="F43" s="10" t="n"/>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="10" t="n"/>
-    </row>
-    <row r="44" ht="31.5" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="F43" s="50" t="n"/>
+      <c r="G43" s="32" t="n"/>
+      <c r="H43" s="50" t="n"/>
+    </row>
+    <row r="44" ht="31.5" customHeight="1" s="27">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>T-37</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n">
+      <c r="B44" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,9)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,9))</f>
         <v/>
       </c>
-      <c r="D44" s="8">
+      <c r="D44" s="37">
         <f>IF('Lisez-moi'!$B$13="","Testeur 3",'Lisez-moi'!$B$13)</f>
         <v/>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="37">
         <f>TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="7" t="n"/>
-      <c r="H44" s="10" t="n"/>
-    </row>
-    <row r="45" ht="31.5" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="F44" s="50" t="n"/>
+      <c r="G44" s="32" t="n"/>
+      <c r="H44" s="50" t="n"/>
+    </row>
+    <row r="45" ht="31.5" customHeight="1" s="27">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>T-38</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n">
+      <c r="B45" s="47" t="n">
         <v>10</v>
       </c>
-      <c r="C45" s="8">
+      <c r="C45" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,10)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,10))</f>
         <v/>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="37">
         <f>IF('Lisez-moi'!$B$13="","Testeur 3",'Lisez-moi'!$B$13)</f>
         <v/>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="37">
         <f>TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
-      <c r="F45" s="10" t="n"/>
-      <c r="G45" s="7" t="n"/>
-      <c r="H45" s="10" t="n"/>
-    </row>
-    <row r="46" ht="31.5" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="F45" s="50" t="n"/>
+      <c r="G45" s="32" t="n"/>
+      <c r="H45" s="50" t="n"/>
+    </row>
+    <row r="46" ht="31.5" customHeight="1" s="27">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>T-39</t>
         </is>
       </c>
-      <c r="B46" s="9" t="n">
+      <c r="B46" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="C46" s="8">
+      <c r="C46" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,11)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,11))</f>
         <v/>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="37">
         <f>IF('Lisez-moi'!$B$13="","Testeur 3",'Lisez-moi'!$B$13)</f>
         <v/>
       </c>
-      <c r="E46" s="8">
+      <c r="E46" s="37">
         <f>TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="7" t="n"/>
-      <c r="H46" s="10" t="n"/>
-    </row>
-    <row r="47" ht="31.5" customHeight="1">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="F46" s="50" t="n"/>
+      <c r="G46" s="32" t="n"/>
+      <c r="H46" s="50" t="n"/>
+    </row>
+    <row r="47" ht="31.5" customHeight="1" s="27">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>T-40</t>
         </is>
       </c>
-      <c r="B47" s="9" t="n">
+      <c r="B47" s="47" t="n">
         <v>12</v>
       </c>
-      <c r="C47" s="8">
+      <c r="C47" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,12)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,12))</f>
         <v/>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="37">
         <f>IF('Lisez-moi'!$B$13="","Testeur 3",'Lisez-moi'!$B$13)</f>
         <v/>
       </c>
-      <c r="E47" s="8">
+      <c r="E47" s="37">
         <f>TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
-      <c r="F47" s="10" t="n"/>
-      <c r="G47" s="7" t="n"/>
-      <c r="H47" s="10" t="n"/>
-    </row>
-    <row r="48" ht="31.5" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="F47" s="50" t="n"/>
+      <c r="G47" s="32" t="n"/>
+      <c r="H47" s="50" t="n"/>
+    </row>
+    <row r="48" ht="31.5" customHeight="1" s="27">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>T-41</t>
         </is>
       </c>
-      <c r="B48" s="9" t="n">
+      <c r="B48" s="47" t="n">
         <v>13</v>
       </c>
-      <c r="C48" s="8">
+      <c r="C48" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,13)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,13))</f>
         <v/>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="37">
         <f>IF('Lisez-moi'!$B$13="","Testeur 3",'Lisez-moi'!$B$13)</f>
         <v/>
       </c>
-      <c r="E48" s="8">
+      <c r="E48" s="37">
         <f>TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
-      <c r="F48" s="10" t="n"/>
-      <c r="G48" s="7" t="n"/>
-      <c r="H48" s="10" t="n"/>
-    </row>
-    <row r="49" ht="31.5" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="F48" s="50" t="n"/>
+      <c r="G48" s="32" t="n"/>
+      <c r="H48" s="50" t="n"/>
+    </row>
+    <row r="49" ht="31.5" customHeight="1" s="27">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>T-42</t>
         </is>
       </c>
-      <c r="B49" s="9" t="n">
+      <c r="B49" s="47" t="n">
         <v>14</v>
       </c>
-      <c r="C49" s="8">
+      <c r="C49" s="37">
         <f>IF(INDEX(Scénarios!$B$5:$B$18,14)="","(scénario personnel à définir)",INDEX(Scénarios!$B$5:$B$18,14))</f>
         <v/>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="37">
         <f>IF('Lisez-moi'!$B$13="","Testeur 3",'Lisez-moi'!$B$13)</f>
         <v/>
       </c>
-      <c r="E49" s="8">
+      <c r="E49" s="37">
         <f>TRIM('Lisez-moi'!$C$13&amp;" "&amp;'Lisez-moi'!$D$13)</f>
         <v/>
       </c>
-      <c r="F49" s="10" t="n"/>
-      <c r="G49" s="7" t="n"/>
-      <c r="H49" s="10" t="n"/>
+      <c r="F49" s="50" t="n"/>
+      <c r="G49" s="32" t="n"/>
+      <c r="H49" s="50" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2521,1352 +2635,1389 @@
     <mergeCell ref="A35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F49">
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
       <formula>F5="Écart"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="0">
+    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
       <formula>F5="Conforme"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="F6:F19 F21:F34 F36:F49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6:F19 F21:F34 F36:F49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Conforme,Écart,Non testé"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="H6:H19 H21:H34 H36:H49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H19 H21:H34 H36:H49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Bloquant,Majeur,Mineur"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <tabColor rgb="FFFF2B47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:I44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" style="26" min="1" max="1"/>
+    <col width="24" customWidth="1" style="26" min="2" max="2"/>
+    <col width="40" customWidth="1" style="26" min="3" max="3"/>
+    <col width="11" customWidth="1" style="26" min="4" max="4"/>
+    <col width="44" customWidth="1" style="26" min="5" max="5"/>
+    <col width="32" customWidth="1" style="26" min="6" max="6"/>
+    <col width="13" customWidth="1" style="26" min="7" max="7"/>
+    <col width="10" customWidth="1" style="26" min="8" max="8"/>
+    <col width="40" customWidth="1" style="26" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="21" customHeight="1" s="27">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Correctifs et validation</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2" ht="14.25" customHeight="1" s="27">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Un écart = une ligne. Corrigez sur main, puis validez en refaisant le scénario EN LIGNE, une fois GitHub Pages passé sur main.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="27">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>ID du test</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>Scénario</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>Écart observé</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>Gravité</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="48" t="inlineStr">
         <is>
           <t>Correctif apporté</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="48" t="inlineStr">
         <is>
           <t>Commit (message)</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="G4" s="48" t="inlineStr">
         <is>
           <t>Date de validation</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="48" t="inlineStr">
         <is>
           <t>Validé?</t>
         </is>
       </c>
-      <c r="I4" s="21" t="inlineStr">
+      <c r="I4" s="48" t="inlineStr">
         <is>
           <t>Comment j'ai validé</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="31.5" customHeight="1">
-      <c r="A5" s="10" t="n"/>
-      <c r="B5" s="8">
+    <row r="5" ht="31.5" customHeight="1" s="27">
+      <c r="A5" s="50" t="n"/>
+      <c r="B5" s="37">
         <f>IF(A5="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A5,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="37">
         <f>IF(A5="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A5,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="47">
         <f>IF(A5="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A5,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="10" t="n"/>
-      <c r="I5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="31.5" customHeight="1">
-      <c r="A6" s="10" t="n"/>
-      <c r="B6" s="8">
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="51" t="n"/>
+      <c r="H5" s="50" t="n"/>
+      <c r="I5" s="32" t="n"/>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" s="27">
+      <c r="A6" s="50" t="n"/>
+      <c r="B6" s="37">
         <f>IF(A6="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A6,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="37">
         <f>IF(A6="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A6,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="47">
         <f>IF(A6="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A6,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="31.5" customHeight="1">
-      <c r="A7" s="10" t="n"/>
-      <c r="B7" s="8">
+      <c r="E6" s="32" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="51" t="n"/>
+      <c r="H6" s="50" t="n"/>
+      <c r="I6" s="32" t="n"/>
+    </row>
+    <row r="7" ht="31.5" customHeight="1" s="27">
+      <c r="A7" s="50" t="n"/>
+      <c r="B7" s="37">
         <f>IF(A7="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A7,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="37">
         <f>IF(A7="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A7,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="47">
         <f>IF(A7="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A7,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="10" t="n"/>
-      <c r="I7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="31.5" customHeight="1">
-      <c r="A8" s="10" t="n"/>
-      <c r="B8" s="8">
+      <c r="E7" s="32" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="51" t="n"/>
+      <c r="H7" s="50" t="n"/>
+      <c r="I7" s="32" t="n"/>
+    </row>
+    <row r="8" ht="31.5" customHeight="1" s="27">
+      <c r="A8" s="50" t="n"/>
+      <c r="B8" s="37">
         <f>IF(A8="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A8,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="37">
         <f>IF(A8="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A8,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="47">
         <f>IF(A8="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A8,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="10" t="n"/>
-      <c r="I8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="31.5" customHeight="1">
-      <c r="A9" s="10" t="n"/>
-      <c r="B9" s="8">
+      <c r="E8" s="32" t="n"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="51" t="n"/>
+      <c r="H8" s="50" t="n"/>
+      <c r="I8" s="32" t="n"/>
+    </row>
+    <row r="9" ht="31.5" customHeight="1" s="27">
+      <c r="A9" s="50" t="n"/>
+      <c r="B9" s="37">
         <f>IF(A9="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A9,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="37">
         <f>IF(A9="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A9,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="47">
         <f>IF(A9="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A9,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="10" t="n"/>
-      <c r="I9" s="7" t="n"/>
-    </row>
-    <row r="10" ht="31.5" customHeight="1">
-      <c r="A10" s="10" t="n"/>
-      <c r="B10" s="8">
+      <c r="E9" s="32" t="n"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="51" t="n"/>
+      <c r="H9" s="50" t="n"/>
+      <c r="I9" s="32" t="n"/>
+    </row>
+    <row r="10" ht="31.5" customHeight="1" s="27">
+      <c r="A10" s="50" t="n"/>
+      <c r="B10" s="37">
         <f>IF(A10="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A10,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="37">
         <f>IF(A10="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A10,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="47">
         <f>IF(A10="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A10,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="7" t="n"/>
-    </row>
-    <row r="11" ht="31.5" customHeight="1">
-      <c r="A11" s="10" t="n"/>
-      <c r="B11" s="8">
+      <c r="E10" s="32" t="n"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="51" t="n"/>
+      <c r="H10" s="50" t="n"/>
+      <c r="I10" s="32" t="n"/>
+    </row>
+    <row r="11" ht="31.5" customHeight="1" s="27">
+      <c r="A11" s="50" t="n"/>
+      <c r="B11" s="37">
         <f>IF(A11="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A11,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="37">
         <f>IF(A11="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A11,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="47">
         <f>IF(A11="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A11,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="10" t="n"/>
-      <c r="I11" s="7" t="n"/>
-    </row>
-    <row r="12" ht="31.5" customHeight="1">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="8">
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="51" t="n"/>
+      <c r="H11" s="50" t="n"/>
+      <c r="I11" s="32" t="n"/>
+    </row>
+    <row r="12" ht="31.5" customHeight="1" s="27">
+      <c r="A12" s="50" t="n"/>
+      <c r="B12" s="37">
         <f>IF(A12="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A12,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="37">
         <f>IF(A12="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A12,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="47">
         <f>IF(A12="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A12,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="7" t="n"/>
-    </row>
-    <row r="13" ht="31.5" customHeight="1">
-      <c r="A13" s="10" t="n"/>
-      <c r="B13" s="8">
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="51" t="n"/>
+      <c r="H12" s="50" t="n"/>
+      <c r="I12" s="32" t="n"/>
+    </row>
+    <row r="13" ht="31.5" customHeight="1" s="27">
+      <c r="A13" s="50" t="n"/>
+      <c r="B13" s="37">
         <f>IF(A13="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A13,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="37">
         <f>IF(A13="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A13,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="47">
         <f>IF(A13="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A13,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="7" t="n"/>
-    </row>
-    <row r="14" ht="31.5" customHeight="1">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="8">
+      <c r="E13" s="32" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="51" t="n"/>
+      <c r="H13" s="50" t="n"/>
+      <c r="I13" s="32" t="n"/>
+    </row>
+    <row r="14" ht="31.5" customHeight="1" s="27">
+      <c r="A14" s="50" t="n"/>
+      <c r="B14" s="37">
         <f>IF(A14="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A14,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="37">
         <f>IF(A14="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A14,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="47">
         <f>IF(A14="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A14,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="31.5" customHeight="1">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="8">
+      <c r="E14" s="32" t="n"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="51" t="n"/>
+      <c r="H14" s="50" t="n"/>
+      <c r="I14" s="32" t="n"/>
+    </row>
+    <row r="15" ht="31.5" customHeight="1" s="27">
+      <c r="A15" s="50" t="n"/>
+      <c r="B15" s="37">
         <f>IF(A15="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A15,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="37">
         <f>IF(A15="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A15,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="47">
         <f>IF(A15="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A15,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="10" t="n"/>
-      <c r="I15" s="7" t="n"/>
-    </row>
-    <row r="16" ht="31.5" customHeight="1">
-      <c r="A16" s="10" t="n"/>
-      <c r="B16" s="8">
+      <c r="E15" s="32" t="n"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="51" t="n"/>
+      <c r="H15" s="50" t="n"/>
+      <c r="I15" s="32" t="n"/>
+    </row>
+    <row r="16" ht="31.5" customHeight="1" s="27">
+      <c r="A16" s="50" t="n"/>
+      <c r="B16" s="37">
         <f>IF(A16="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A16,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="37">
         <f>IF(A16="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A16,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="47">
         <f>IF(A16="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A16,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="10" t="n"/>
-      <c r="I16" s="7" t="n"/>
-    </row>
-    <row r="17" ht="31.5" customHeight="1">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="8">
+      <c r="E16" s="32" t="n"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="51" t="n"/>
+      <c r="H16" s="50" t="n"/>
+      <c r="I16" s="32" t="n"/>
+    </row>
+    <row r="17" ht="31.5" customHeight="1" s="27">
+      <c r="A17" s="50" t="n"/>
+      <c r="B17" s="37">
         <f>IF(A17="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A17,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="37">
         <f>IF(A17="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A17,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="47">
         <f>IF(A17="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A17,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="7" t="n"/>
-    </row>
-    <row r="18" ht="31.5" customHeight="1">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="8">
+      <c r="E17" s="32" t="n"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="51" t="n"/>
+      <c r="H17" s="50" t="n"/>
+      <c r="I17" s="32" t="n"/>
+    </row>
+    <row r="18" ht="31.5" customHeight="1" s="27">
+      <c r="A18" s="50" t="n"/>
+      <c r="B18" s="37">
         <f>IF(A18="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A18,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="37">
         <f>IF(A18="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A18,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="47">
         <f>IF(A18="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A18,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="7" t="n"/>
-    </row>
-    <row r="19" ht="31.5" customHeight="1">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="8">
+      <c r="E18" s="32" t="n"/>
+      <c r="F18" s="32" t="n"/>
+      <c r="G18" s="51" t="n"/>
+      <c r="H18" s="50" t="n"/>
+      <c r="I18" s="32" t="n"/>
+    </row>
+    <row r="19" ht="31.5" customHeight="1" s="27">
+      <c r="A19" s="50" t="n"/>
+      <c r="B19" s="37">
         <f>IF(A19="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A19,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="37">
         <f>IF(A19="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A19,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="47">
         <f>IF(A19="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A19,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="7" t="n"/>
-    </row>
-    <row r="20" ht="31.5" customHeight="1">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="8">
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="51" t="n"/>
+      <c r="H19" s="50" t="n"/>
+      <c r="I19" s="32" t="n"/>
+    </row>
+    <row r="20" ht="31.5" customHeight="1" s="27">
+      <c r="A20" s="50" t="n"/>
+      <c r="B20" s="37">
         <f>IF(A20="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A20,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="37">
         <f>IF(A20="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A20,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="47">
         <f>IF(A20="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A20,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="31.5" customHeight="1">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="8">
+      <c r="E20" s="32" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="51" t="n"/>
+      <c r="H20" s="50" t="n"/>
+      <c r="I20" s="32" t="n"/>
+    </row>
+    <row r="21" ht="31.5" customHeight="1" s="27">
+      <c r="A21" s="50" t="n"/>
+      <c r="B21" s="37">
         <f>IF(A21="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A21,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="37">
         <f>IF(A21="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A21,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="47">
         <f>IF(A21="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A21,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="31.5" customHeight="1">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="8">
+      <c r="E21" s="32" t="n"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="51" t="n"/>
+      <c r="H21" s="50" t="n"/>
+      <c r="I21" s="32" t="n"/>
+    </row>
+    <row r="22" ht="31.5" customHeight="1" s="27">
+      <c r="A22" s="50" t="n"/>
+      <c r="B22" s="37">
         <f>IF(A22="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A22,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="37">
         <f>IF(A22="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A22,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="47">
         <f>IF(A22="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A22,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="7" t="n"/>
-    </row>
-    <row r="23" ht="31.5" customHeight="1">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="8">
+      <c r="E22" s="32" t="n"/>
+      <c r="F22" s="32" t="n"/>
+      <c r="G22" s="51" t="n"/>
+      <c r="H22" s="50" t="n"/>
+      <c r="I22" s="32" t="n"/>
+    </row>
+    <row r="23" ht="31.5" customHeight="1" s="27">
+      <c r="A23" s="50" t="n"/>
+      <c r="B23" s="37">
         <f>IF(A23="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A23,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="37">
         <f>IF(A23="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A23,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="47">
         <f>IF(A23="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A23,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="10" t="n"/>
-      <c r="I23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="31.5" customHeight="1">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="8">
+      <c r="E23" s="32" t="n"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="51" t="n"/>
+      <c r="H23" s="50" t="n"/>
+      <c r="I23" s="32" t="n"/>
+    </row>
+    <row r="24" ht="31.5" customHeight="1" s="27">
+      <c r="A24" s="50" t="n"/>
+      <c r="B24" s="37">
         <f>IF(A24="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A24,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="37">
         <f>IF(A24="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A24,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="47">
         <f>IF(A24="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A24,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="10" t="n"/>
-      <c r="I24" s="7" t="n"/>
-    </row>
-    <row r="25" ht="31.5" customHeight="1">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="8">
+      <c r="E24" s="32" t="n"/>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="51" t="n"/>
+      <c r="H24" s="50" t="n"/>
+      <c r="I24" s="32" t="n"/>
+    </row>
+    <row r="25" ht="31.5" customHeight="1" s="27">
+      <c r="A25" s="50" t="n"/>
+      <c r="B25" s="37">
         <f>IF(A25="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A25,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="37">
         <f>IF(A25="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A25,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="47">
         <f>IF(A25="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A25,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="10" t="n"/>
-      <c r="I25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="31.5" customHeight="1">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="8">
+      <c r="E25" s="32" t="n"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="51" t="n"/>
+      <c r="H25" s="50" t="n"/>
+      <c r="I25" s="32" t="n"/>
+    </row>
+    <row r="26" ht="31.5" customHeight="1" s="27">
+      <c r="A26" s="50" t="n"/>
+      <c r="B26" s="37">
         <f>IF(A26="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A26,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="37">
         <f>IF(A26="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A26,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="47">
         <f>IF(A26="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A26,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="10" t="n"/>
-      <c r="I26" s="7" t="n"/>
-    </row>
-    <row r="27" ht="31.5" customHeight="1">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="8">
+      <c r="E26" s="32" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="51" t="n"/>
+      <c r="H26" s="50" t="n"/>
+      <c r="I26" s="32" t="n"/>
+    </row>
+    <row r="27" ht="31.5" customHeight="1" s="27">
+      <c r="A27" s="50" t="n"/>
+      <c r="B27" s="37">
         <f>IF(A27="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A27,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="37">
         <f>IF(A27="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A27,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="47">
         <f>IF(A27="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A27,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="10" t="n"/>
-      <c r="I27" s="7" t="n"/>
-    </row>
-    <row r="28" ht="31.5" customHeight="1">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="8">
+      <c r="E27" s="32" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="51" t="n"/>
+      <c r="H27" s="50" t="n"/>
+      <c r="I27" s="32" t="n"/>
+    </row>
+    <row r="28" ht="31.5" customHeight="1" s="27">
+      <c r="A28" s="50" t="n"/>
+      <c r="B28" s="37">
         <f>IF(A28="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A28,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="37">
         <f>IF(A28="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A28,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="47">
         <f>IF(A28="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A28,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="7" t="n"/>
-    </row>
-    <row r="29" ht="31.5" customHeight="1">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="8">
+      <c r="E28" s="32" t="n"/>
+      <c r="F28" s="32" t="n"/>
+      <c r="G28" s="51" t="n"/>
+      <c r="H28" s="50" t="n"/>
+      <c r="I28" s="32" t="n"/>
+    </row>
+    <row r="29" ht="31.5" customHeight="1" s="27">
+      <c r="A29" s="50" t="n"/>
+      <c r="B29" s="37">
         <f>IF(A29="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A29,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="37">
         <f>IF(A29="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A29,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="47">
         <f>IF(A29="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A29,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="10" t="n"/>
-      <c r="I29" s="7" t="n"/>
-    </row>
-    <row r="30" ht="31.5" customHeight="1">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="8">
+      <c r="E29" s="32" t="n"/>
+      <c r="F29" s="32" t="n"/>
+      <c r="G29" s="51" t="n"/>
+      <c r="H29" s="50" t="n"/>
+      <c r="I29" s="32" t="n"/>
+    </row>
+    <row r="30" ht="31.5" customHeight="1" s="27">
+      <c r="A30" s="50" t="n"/>
+      <c r="B30" s="37">
         <f>IF(A30="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A30,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="37">
         <f>IF(A30="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A30,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="47">
         <f>IF(A30="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A30,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="10" t="n"/>
-      <c r="I30" s="7" t="n"/>
-    </row>
-    <row r="31" ht="31.5" customHeight="1">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="8">
+      <c r="E30" s="32" t="n"/>
+      <c r="F30" s="32" t="n"/>
+      <c r="G30" s="51" t="n"/>
+      <c r="H30" s="50" t="n"/>
+      <c r="I30" s="32" t="n"/>
+    </row>
+    <row r="31" ht="31.5" customHeight="1" s="27">
+      <c r="A31" s="50" t="n"/>
+      <c r="B31" s="37">
         <f>IF(A31="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A31,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="37">
         <f>IF(A31="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A31,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="47">
         <f>IF(A31="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A31,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="10" t="n"/>
-      <c r="I31" s="7" t="n"/>
-    </row>
-    <row r="32" ht="31.5" customHeight="1">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="8">
+      <c r="E31" s="32" t="n"/>
+      <c r="F31" s="32" t="n"/>
+      <c r="G31" s="51" t="n"/>
+      <c r="H31" s="50" t="n"/>
+      <c r="I31" s="32" t="n"/>
+    </row>
+    <row r="32" ht="31.5" customHeight="1" s="27">
+      <c r="A32" s="50" t="n"/>
+      <c r="B32" s="37">
         <f>IF(A32="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A32,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="37">
         <f>IF(A32="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A32,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="47">
         <f>IF(A32="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A32,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="7" t="n"/>
-    </row>
-    <row r="33" ht="31.5" customHeight="1">
-      <c r="A33" s="10" t="n"/>
-      <c r="B33" s="8">
+      <c r="E32" s="32" t="n"/>
+      <c r="F32" s="32" t="n"/>
+      <c r="G32" s="51" t="n"/>
+      <c r="H32" s="50" t="n"/>
+      <c r="I32" s="32" t="n"/>
+    </row>
+    <row r="33" ht="31.5" customHeight="1" s="27">
+      <c r="A33" s="50" t="n"/>
+      <c r="B33" s="37">
         <f>IF(A33="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A33,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="37">
         <f>IF(A33="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A33,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="47">
         <f>IF(A33="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A33,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="10" t="n"/>
-      <c r="I33" s="7" t="n"/>
-    </row>
-    <row r="34" ht="31.5" customHeight="1">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="8">
+      <c r="E33" s="32" t="n"/>
+      <c r="F33" s="32" t="n"/>
+      <c r="G33" s="51" t="n"/>
+      <c r="H33" s="50" t="n"/>
+      <c r="I33" s="32" t="n"/>
+    </row>
+    <row r="34" ht="31.5" customHeight="1" s="27">
+      <c r="A34" s="50" t="n"/>
+      <c r="B34" s="37">
         <f>IF(A34="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A34,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="37">
         <f>IF(A34="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A34,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="47">
         <f>IF(A34="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A34,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="11" t="n"/>
-      <c r="H34" s="10" t="n"/>
-      <c r="I34" s="7" t="n"/>
-    </row>
-    <row r="35" ht="31.5" customHeight="1">
-      <c r="A35" s="10" t="n"/>
-      <c r="B35" s="8">
+      <c r="E34" s="32" t="n"/>
+      <c r="F34" s="32" t="n"/>
+      <c r="G34" s="51" t="n"/>
+      <c r="H34" s="50" t="n"/>
+      <c r="I34" s="32" t="n"/>
+    </row>
+    <row r="35" ht="31.5" customHeight="1" s="27">
+      <c r="A35" s="50" t="n"/>
+      <c r="B35" s="37">
         <f>IF(A35="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A35,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="37">
         <f>IF(A35="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A35,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="47">
         <f>IF(A35="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A35,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="7" t="n"/>
-    </row>
-    <row r="36" ht="31.5" customHeight="1">
-      <c r="A36" s="10" t="n"/>
-      <c r="B36" s="8">
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="51" t="n"/>
+      <c r="H35" s="50" t="n"/>
+      <c r="I35" s="32" t="n"/>
+    </row>
+    <row r="36" ht="31.5" customHeight="1" s="27">
+      <c r="A36" s="50" t="n"/>
+      <c r="B36" s="37">
         <f>IF(A36="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A36,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="37">
         <f>IF(A36="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A36,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="47">
         <f>IF(A36="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A36,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="10" t="n"/>
-      <c r="I36" s="7" t="n"/>
-    </row>
-    <row r="37" ht="31.5" customHeight="1">
-      <c r="A37" s="10" t="n"/>
-      <c r="B37" s="8">
+      <c r="E36" s="32" t="n"/>
+      <c r="F36" s="32" t="n"/>
+      <c r="G36" s="51" t="n"/>
+      <c r="H36" s="50" t="n"/>
+      <c r="I36" s="32" t="n"/>
+    </row>
+    <row r="37" ht="31.5" customHeight="1" s="27">
+      <c r="A37" s="50" t="n"/>
+      <c r="B37" s="37">
         <f>IF(A37="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A37,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="37">
         <f>IF(A37="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A37,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="47">
         <f>IF(A37="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A37,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="7" t="n"/>
-    </row>
-    <row r="38" ht="31.5" customHeight="1">
-      <c r="A38" s="10" t="n"/>
-      <c r="B38" s="8">
+      <c r="E37" s="32" t="n"/>
+      <c r="F37" s="32" t="n"/>
+      <c r="G37" s="51" t="n"/>
+      <c r="H37" s="50" t="n"/>
+      <c r="I37" s="32" t="n"/>
+    </row>
+    <row r="38" ht="31.5" customHeight="1" s="27">
+      <c r="A38" s="50" t="n"/>
+      <c r="B38" s="37">
         <f>IF(A38="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A38,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="37">
         <f>IF(A38="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A38,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="47">
         <f>IF(A38="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A38,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="11" t="n"/>
-      <c r="H38" s="10" t="n"/>
-      <c r="I38" s="7" t="n"/>
-    </row>
-    <row r="39" ht="31.5" customHeight="1">
-      <c r="A39" s="10" t="n"/>
-      <c r="B39" s="8">
+      <c r="E38" s="32" t="n"/>
+      <c r="F38" s="32" t="n"/>
+      <c r="G38" s="51" t="n"/>
+      <c r="H38" s="50" t="n"/>
+      <c r="I38" s="32" t="n"/>
+    </row>
+    <row r="39" ht="31.5" customHeight="1" s="27">
+      <c r="A39" s="50" t="n"/>
+      <c r="B39" s="37">
         <f>IF(A39="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A39,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C39" s="8">
+      <c r="C39" s="37">
         <f>IF(A39="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A39,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="47">
         <f>IF(A39="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A39,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
-      <c r="G39" s="11" t="n"/>
-      <c r="H39" s="10" t="n"/>
-      <c r="I39" s="7" t="n"/>
-    </row>
-    <row r="40" ht="31.5" customHeight="1">
-      <c r="A40" s="10" t="n"/>
-      <c r="B40" s="8">
+      <c r="E39" s="32" t="n"/>
+      <c r="F39" s="32" t="n"/>
+      <c r="G39" s="51" t="n"/>
+      <c r="H39" s="50" t="n"/>
+      <c r="I39" s="32" t="n"/>
+    </row>
+    <row r="40" ht="31.5" customHeight="1" s="27">
+      <c r="A40" s="50" t="n"/>
+      <c r="B40" s="37">
         <f>IF(A40="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A40,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C40" s="8">
+      <c r="C40" s="37">
         <f>IF(A40="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A40,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="47">
         <f>IF(A40="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A40,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
-      <c r="G40" s="11" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="7" t="n"/>
-    </row>
-    <row r="41" ht="31.5" customHeight="1">
-      <c r="A41" s="10" t="n"/>
-      <c r="B41" s="8">
+      <c r="E40" s="32" t="n"/>
+      <c r="F40" s="32" t="n"/>
+      <c r="G40" s="51" t="n"/>
+      <c r="H40" s="50" t="n"/>
+      <c r="I40" s="32" t="n"/>
+    </row>
+    <row r="41" ht="31.5" customHeight="1" s="27">
+      <c r="A41" s="50" t="n"/>
+      <c r="B41" s="37">
         <f>IF(A41="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A41,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C41" s="8">
+      <c r="C41" s="37">
         <f>IF(A41="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A41,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="47">
         <f>IF(A41="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A41,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="10" t="n"/>
-      <c r="I41" s="7" t="n"/>
-    </row>
-    <row r="42" ht="31.5" customHeight="1">
-      <c r="A42" s="10" t="n"/>
-      <c r="B42" s="8">
+      <c r="E41" s="32" t="n"/>
+      <c r="F41" s="32" t="n"/>
+      <c r="G41" s="51" t="n"/>
+      <c r="H41" s="50" t="n"/>
+      <c r="I41" s="32" t="n"/>
+    </row>
+    <row r="42" ht="31.5" customHeight="1" s="27">
+      <c r="A42" s="50" t="n"/>
+      <c r="B42" s="37">
         <f>IF(A42="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A42,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C42" s="8">
+      <c r="C42" s="37">
         <f>IF(A42="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A42,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="47">
         <f>IF(A42="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A42,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
-      <c r="G42" s="11" t="n"/>
-      <c r="H42" s="10" t="n"/>
-      <c r="I42" s="7" t="n"/>
-    </row>
-    <row r="43" ht="31.5" customHeight="1">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="8">
+      <c r="E42" s="32" t="n"/>
+      <c r="F42" s="32" t="n"/>
+      <c r="G42" s="51" t="n"/>
+      <c r="H42" s="50" t="n"/>
+      <c r="I42" s="32" t="n"/>
+    </row>
+    <row r="43" ht="31.5" customHeight="1" s="27">
+      <c r="A43" s="50" t="n"/>
+      <c r="B43" s="37">
         <f>IF(A43="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A43,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C43" s="8">
+      <c r="C43" s="37">
         <f>IF(A43="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A43,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="47">
         <f>IF(A43="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A43,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
-      <c r="G43" s="11" t="n"/>
-      <c r="H43" s="10" t="n"/>
-      <c r="I43" s="7" t="n"/>
-    </row>
-    <row r="44" ht="31.5" customHeight="1">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="8">
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="51" t="n"/>
+      <c r="H43" s="50" t="n"/>
+      <c r="I43" s="32" t="n"/>
+    </row>
+    <row r="44" ht="31.5" customHeight="1" s="27">
+      <c r="A44" s="50" t="n"/>
+      <c r="B44" s="37">
         <f>IF(A44="","",IFERROR(INDEX(Tests!$C$5:$C$49,MATCH(A44,Tests!$A$5:$A$49,0)),"ID introuvable"))</f>
         <v/>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="37">
         <f>IF(A44="","",IFERROR(INDEX(Tests!$G$5:$G$49,MATCH(A44,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="47">
         <f>IF(A44="","",IFERROR(INDEX(Tests!$H$5:$H$49,MATCH(A44,Tests!$A$5:$A$49,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="E44" s="7" t="n"/>
-      <c r="F44" s="7" t="n"/>
-      <c r="G44" s="11" t="n"/>
-      <c r="H44" s="10" t="n"/>
-      <c r="I44" s="7" t="n"/>
+      <c r="E44" s="32" t="n"/>
+      <c r="F44" s="32" t="n"/>
+      <c r="G44" s="51" t="n"/>
+      <c r="H44" s="50" t="n"/>
+      <c r="I44" s="32" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Oui,Non,Pas corrigé (justifié)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <tabColor rgb="FF0A0A0A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" style="26" min="1" max="1"/>
+    <col width="52" customWidth="1" style="26" min="2" max="2"/>
+    <col width="14" customWidth="1" style="26" min="3" max="3"/>
+    <col width="60" customWidth="1" style="26" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="21" customHeight="1" s="27">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Autoévaluation avec la grille critériée</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2" ht="14.25" customHeight="1" s="27">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>À faire à la maison. Pour chaque indicateur : votre niveau, et la preuve qui le justifie (fichier, ligne du tableau, commit...).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="27">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>Critère</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>Indicateur</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>Mon niveau</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>Preuve / justification</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="43.5" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5" ht="43.5" customHeight="1" s="27">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>C1 Conception (/15)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Interface cohérente sur le plan visuel (couleurs, typographie, hiérarchie) qui reflète l'identité du portfolio</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="43.5" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="C5" s="50" t="n"/>
+      <c r="D5" s="32" t="n"/>
+    </row>
+    <row r="6" ht="43.5" customHeight="1" s="27">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>C1 Conception (/15)</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Arborescence et structure des pages, démontrées par le document de planification</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="43.5" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="C6" s="50" t="n"/>
+      <c r="D6" s="32" t="n"/>
+    </row>
+    <row r="7" ht="43.5" customHeight="1" s="27">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>C1 Conception (/15)</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Justification de chaque technologie choisie</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="43.5" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="C7" s="50" t="n"/>
+      <c r="D7" s="32" t="n"/>
+    </row>
+    <row r="8" ht="43.5" customHeight="1" s="27">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>C1 Conception (/15)</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Structure de dossiers cohérente et convention de nommage uniforme</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="43.5" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="C8" s="50" t="n"/>
+      <c r="D8" s="32" t="n"/>
+    </row>
+    <row r="9" ht="43.5" customHeight="1" s="27">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>C1 Conception (/15)</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Traitement optimisé des médias (format, compression, dimensions)</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="7" t="n"/>
-    </row>
-    <row r="10" ht="43.5" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="C9" s="50" t="n"/>
+      <c r="D9" s="32" t="n"/>
+    </row>
+    <row r="10" ht="43.5" customHeight="1" s="27">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>C1 Conception (/15)</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>Justification orale devant le jury (à anticiper : quelles questions pourrait-on vous poser?)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="7" t="n"/>
-    </row>
-    <row r="11" ht="43.5" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="C10" s="50" t="n"/>
+      <c r="D10" s="32" t="n"/>
+    </row>
+    <row r="11" ht="43.5" customHeight="1" s="27">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>C2 Programmation (/15)</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Mise en page flexible et adaptative (mobile, tablette, ordinateur)</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="7" t="n"/>
-    </row>
-    <row r="12" ht="43.5" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="C11" s="50" t="n"/>
+      <c r="D11" s="32" t="n"/>
+    </row>
+    <row r="12" ht="43.5" customHeight="1" s="27">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>C2 Programmation (/15)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Navigation et éléments interactifs fonctionnels, sans erreur bloquante</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="7" t="n"/>
-    </row>
-    <row r="13" ht="43.5" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="C12" s="50" t="n"/>
+      <c r="D12" s="32" t="n"/>
+    </row>
+    <row r="13" ht="43.5" customHeight="1" s="27">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>C2 Programmation (/15)</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Normes d'accessibilité WCAG AA (sémantique, alt, contraste, clavier)</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="7" t="n"/>
-    </row>
-    <row r="14" ht="43.5" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="C13" s="50" t="n"/>
+      <c r="D13" s="32" t="n"/>
+    </row>
+    <row r="14" ht="43.5" customHeight="1" s="27">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>C2 Programmation (/15)</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>Commentaires pertinents (HTML, CSS, JS)</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="43.5" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="C14" s="50" t="n"/>
+      <c r="D14" s="32" t="n"/>
+    </row>
+    <row r="15" ht="43.5" customHeight="1" s="27">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>C2 Programmation (/15)</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Chargement efficace des données (peu de duplication, chargement perçu rapide)</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="7" t="n"/>
-    </row>
-    <row r="16" ht="43.5" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="C15" s="50" t="n"/>
+      <c r="D15" s="32" t="n"/>
+    </row>
+    <row r="16" ht="43.5" customHeight="1" s="27">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>C3 Contrôle de la qualité (/10)</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>Vérification de l'expérience et du fonctionnement auprès de 3 personnes, chacune sur un environnement différent</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="7" t="n"/>
-    </row>
-    <row r="17" ht="43.5" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="C16" s="50" t="n"/>
+      <c r="D16" s="32" t="n"/>
+    </row>
+    <row r="17" ht="43.5" customHeight="1" s="27">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>C3 Contrôle de la qualité (/10)</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>Rapport de tests : scénario, résultat observé, écart</t>
         </is>
       </c>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="7" t="n"/>
-    </row>
-    <row r="18" ht="43.5" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="C17" s="50" t="n"/>
+      <c r="D17" s="32" t="n"/>
+    </row>
+    <row r="18" ht="43.5" customHeight="1" s="27">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>C3 Contrôle de la qualité (/10)</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Correctifs adéquats, décrits et validés</t>
         </is>
       </c>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="7" t="n"/>
+      <c r="C18" s="50" t="n"/>
+      <c r="D18" s="32" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C5:C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Insuffisant,Acceptable,Très bien,Excellent"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <tabColor rgb="FF0A0A0A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" style="26" min="1" max="1"/>
+    <col width="14" customWidth="1" style="26" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="21" customHeight="1" s="27">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Synthèse</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2" ht="14.25" customHeight="1" s="27">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Calculée automatiquement à partir des onglets Tests et Correctifs.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="27">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>Indicateur</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>Valeur</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5" ht="14.25" customHeight="1" s="27">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Lignes de test</t>
         </is>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="47">
         <f>COUNTA(Tests!A5:A49)-3</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6" ht="14.25" customHeight="1" s="27">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Tests faits (Conforme ou Écart)</t>
         </is>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="47">
         <f>COUNTIF(Tests!F5:F49,"Conforme")+COUNTIF(Tests!F5:F49,"Écart")</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7" ht="14.25" customHeight="1" s="27">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   par le testeur 1</t>
+        </is>
+      </c>
+      <c r="B7" s="47">
+        <f>COUNTIF(Tests!F6:F19,"Conforme")+COUNTIF(Tests!F6:F19,"Écart")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1" s="27">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   par le testeur 2</t>
+        </is>
+      </c>
+      <c r="B8" s="47">
+        <f>COUNTIF(Tests!F21:F34,"Conforme")+COUNTIF(Tests!F21:F34,"Écart")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1" s="27">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   par le testeur 3</t>
+        </is>
+      </c>
+      <c r="B9" s="47">
+        <f>COUNTIF(Tests!F36:F49,"Conforme")+COUNTIF(Tests!F36:F49,"Écart")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1" s="27">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Conformes</t>
         </is>
       </c>
-      <c r="B7" s="9">
+      <c r="B10" s="47">
         <f>COUNTIF(Tests!F5:F49,"Conforme")</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="11" ht="14.25" customHeight="1" s="27">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Écarts</t>
         </is>
       </c>
-      <c r="B8" s="9">
+      <c r="B11" s="47">
         <f>COUNTIF(Tests!F5:F49,"Écart")</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="12" ht="14.25" customHeight="1" s="27">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">   dont bloquants</t>
         </is>
       </c>
-      <c r="B9" s="9">
+      <c r="B12" s="47">
         <f>COUNTIFS(Tests!F5:F49,"Écart",Tests!H5:H49,"Bloquant")</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="13" ht="14.25" customHeight="1" s="27">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">   dont majeurs</t>
         </is>
       </c>
-      <c r="B10" s="9">
+      <c r="B13" s="47">
         <f>COUNTIFS(Tests!F5:F49,"Écart",Tests!H5:H49,"Majeur")</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="14" ht="14.25" customHeight="1" s="27">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">   dont mineurs</t>
         </is>
       </c>
-      <c r="B11" s="9">
+      <c r="B14" s="47">
         <f>COUNTIFS(Tests!F5:F49,"Écart",Tests!H5:H49,"Mineur")</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="15" ht="14.25" customHeight="1" s="27">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>Écarts sans gravité (à compléter)</t>
         </is>
       </c>
-      <c r="B12" s="9">
-        <f>B8-B9-B10-B11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="B15" s="47">
+        <f>B11-B12-B13-B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1" s="27">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>Correctifs inscrits</t>
         </is>
       </c>
-      <c r="B13" s="9">
+      <c r="B16" s="47">
         <f>COUNTA(Correctifs!A5:A44)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="17" ht="22.5" customHeight="1" s="27">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>Correctifs validés</t>
         </is>
       </c>
-      <c r="B14" s="9">
+      <c r="B17" s="47">
         <f>COUNTIF(Correctifs!H5:H44,"Oui")</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="18" ht="14.25" customHeight="1" s="27">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>Écarts validés (%)</t>
         </is>
       </c>
-      <c r="B15" s="12">
-        <f>IF(B8=0,0,B14/B8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="22.8" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="B18" s="52">
+        <f>IF(B11=0,0,B17/B11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="21.75" customHeight="1" s="27">
+      <c r="A20" s="53" t="inlineStr">
         <is>
           <t>Note : « Lignes de test » exclut les 3 bandeaux de testeurs.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>